--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 1</t>
+    <t>Parcial Rodada 2</t>
   </si>
   <si>
     <t>time_id</t>
@@ -612,10 +612,10 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>68.06</v>
+        <v>68.06005859375</v>
+      </c>
+      <c r="D2">
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -626,10 +626,10 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>53.66</v>
+        <v>53.659912109375</v>
+      </c>
+      <c r="D3">
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -640,10 +640,10 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>66.86</v>
+        <v>66.85986328125</v>
+      </c>
+      <c r="D4">
+        <v>66.85986328125</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -654,9 +654,9 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="V5">
+        <v>70</v>
+      </c>
+      <c r="D5">
         <v>70</v>
       </c>
     </row>
@@ -668,10 +668,10 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>58.96</v>
+        <v>58.9599609375</v>
+      </c>
+      <c r="D6">
+        <v>58.9599609375</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -682,10 +682,10 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>57.45</v>
+        <v>57.449951171875</v>
+      </c>
+      <c r="D7">
+        <v>57.449951171875</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -696,10 +696,10 @@
         <v>28</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>68.06</v>
+        <v>68.06005859375</v>
+      </c>
+      <c r="D8">
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -710,10 +710,10 @@
         <v>29</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>47.86</v>
+        <v>47.860107421875</v>
+      </c>
+      <c r="D9">
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -724,10 +724,10 @@
         <v>30</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>64.56</v>
+        <v>64.56005859375</v>
+      </c>
+      <c r="D10">
+        <v>64.56005859375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -738,10 +738,10 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>44.26</v>
+        <v>44.260009765625</v>
+      </c>
+      <c r="D11">
+        <v>44.260009765625</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -752,10 +752,10 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>61.56</v>
+        <v>61.56005859375</v>
+      </c>
+      <c r="D12">
+        <v>61.56005859375</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -766,10 +766,10 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>84.86</v>
+        <v>84.85986328125</v>
+      </c>
+      <c r="D13">
+        <v>84.85986328125</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -780,10 +780,7 @@
         <v>34</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>42.96</v>
+        <v>42.9599609375</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -794,10 +791,10 @@
         <v>35</v>
       </c>
       <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>74.06</v>
+        <v>74.06005859375</v>
+      </c>
+      <c r="D15">
+        <v>74.06005859375</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -808,13 +805,13 @@
         <v>36</v>
       </c>
       <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>54.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>54.60009765625</v>
+      </c>
+      <c r="D16">
+        <v>54.60009765625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -822,13 +819,13 @@
         <v>37</v>
       </c>
       <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>84.26000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>84.259765625</v>
+      </c>
+      <c r="D17">
+        <v>84.259765625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -836,13 +833,13 @@
         <v>38</v>
       </c>
       <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="V18">
         <v>59.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="D18">
+        <v>59.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -850,13 +847,13 @@
         <v>39</v>
       </c>
       <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>54.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>54.159912109375</v>
+      </c>
+      <c r="D19">
+        <v>54.159912109375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -864,13 +861,13 @@
         <v>40</v>
       </c>
       <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>63.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>63.89990234375</v>
+      </c>
+      <c r="D20">
+        <v>63.89990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -878,13 +875,13 @@
         <v>41</v>
       </c>
       <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>50.26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+        <v>50.260009765625</v>
+      </c>
+      <c r="D21">
+        <v>50.260009765625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -892,13 +889,13 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>73.95999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>73.9599609375</v>
+      </c>
+      <c r="D22">
+        <v>73.9599609375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -906,13 +903,13 @@
         <v>43</v>
       </c>
       <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>72.7001953125</v>
+      </c>
+      <c r="D23">
+        <v>72.7001953125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -920,13 +917,13 @@
         <v>44</v>
       </c>
       <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>57.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>57.60009765625</v>
+      </c>
+      <c r="D24">
+        <v>57.60009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -934,13 +931,13 @@
         <v>45</v>
       </c>
       <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>64.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>64.7001953125</v>
+      </c>
+      <c r="D25">
+        <v>64.7001953125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -948,13 +945,13 @@
         <v>46</v>
       </c>
       <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>44.06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+        <v>44.06005859375</v>
+      </c>
+      <c r="D26">
+        <v>44.06005859375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -962,13 +959,13 @@
         <v>47</v>
       </c>
       <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="V27">
         <v>49</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="D27">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -976,13 +973,13 @@
         <v>48</v>
       </c>
       <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>61.96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>61.9599609375</v>
+      </c>
+      <c r="D28">
+        <v>61.9599609375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -990,13 +987,13 @@
         <v>49</v>
       </c>
       <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>60.159912109375</v>
+      </c>
+      <c r="D29">
+        <v>60.159912109375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1004,13 +1001,13 @@
         <v>50</v>
       </c>
       <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>62.56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>62.56005859375</v>
+      </c>
+      <c r="D30">
+        <v>62.56005859375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1018,13 +1015,13 @@
         <v>51</v>
       </c>
       <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>73.76000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>73.759765625</v>
+      </c>
+      <c r="D31">
+        <v>73.759765625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1032,13 +1029,13 @@
         <v>52</v>
       </c>
       <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>64.56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>64.56005859375</v>
+      </c>
+      <c r="D32">
+        <v>64.56005859375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1046,10 +1043,10 @@
         <v>53</v>
       </c>
       <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>47.86</v>
+        <v>47.860107421875</v>
+      </c>
+      <c r="D33">
+        <v>47.860107421875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -617,6 +617,9 @@
       <c r="D2">
         <v>68.06005859375</v>
       </c>
+      <c r="V2">
+        <v>58.3</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -631,6 +634,9 @@
       <c r="D3">
         <v>53.659912109375</v>
       </c>
+      <c r="V3">
+        <v>49.8</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -645,6 +651,9 @@
       <c r="D4">
         <v>66.85986328125</v>
       </c>
+      <c r="V4">
+        <v>50.35</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -659,6 +668,9 @@
       <c r="D5">
         <v>70</v>
       </c>
+      <c r="V5">
+        <v>63.25</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -673,6 +685,9 @@
       <c r="D6">
         <v>58.9599609375</v>
       </c>
+      <c r="V6">
+        <v>38.8</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -687,6 +702,9 @@
       <c r="D7">
         <v>57.449951171875</v>
       </c>
+      <c r="V7">
+        <v>35.75</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -701,6 +719,9 @@
       <c r="D8">
         <v>68.06005859375</v>
       </c>
+      <c r="V8">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -715,6 +736,9 @@
       <c r="D9">
         <v>47.860107421875</v>
       </c>
+      <c r="V9">
+        <v>52.8</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -729,6 +753,9 @@
       <c r="D10">
         <v>64.56005859375</v>
       </c>
+      <c r="V10">
+        <v>62.25</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -743,6 +770,9 @@
       <c r="D11">
         <v>44.260009765625</v>
       </c>
+      <c r="V11">
+        <v>46.35</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -757,6 +787,9 @@
       <c r="D12">
         <v>61.56005859375</v>
       </c>
+      <c r="V12">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -771,6 +804,9 @@
       <c r="D13">
         <v>84.85986328125</v>
       </c>
+      <c r="V13">
+        <v>45.15</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -782,6 +818,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>62.4</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -796,6 +835,9 @@
       <c r="D15">
         <v>74.06005859375</v>
       </c>
+      <c r="V15">
+        <v>83.55</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -810,8 +852,11 @@
       <c r="D16">
         <v>54.60009765625</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="V16">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -824,8 +869,11 @@
       <c r="D17">
         <v>84.259765625</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="V17">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -838,8 +886,11 @@
       <c r="D18">
         <v>59.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="V18">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -852,8 +903,11 @@
       <c r="D19">
         <v>54.159912109375</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="V19">
+        <v>59.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -866,8 +920,11 @@
       <c r="D20">
         <v>63.89990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="V20">
+        <v>63.55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -880,8 +937,11 @@
       <c r="D21">
         <v>50.260009765625</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="V21">
+        <v>37.55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -894,8 +954,11 @@
       <c r="D22">
         <v>73.9599609375</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="V22">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -908,8 +971,11 @@
       <c r="D23">
         <v>72.7001953125</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="V23">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -922,8 +988,11 @@
       <c r="D24">
         <v>57.60009765625</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="V24">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -936,8 +1005,11 @@
       <c r="D25">
         <v>64.7001953125</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="V25">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -950,8 +1022,11 @@
       <c r="D26">
         <v>44.06005859375</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="V26">
+        <v>75.05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -964,8 +1039,11 @@
       <c r="D27">
         <v>49</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="V27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -978,8 +1056,11 @@
       <c r="D28">
         <v>61.9599609375</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="V28">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -992,8 +1073,11 @@
       <c r="D29">
         <v>60.159912109375</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="V29">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1006,8 +1090,11 @@
       <c r="D30">
         <v>62.56005859375</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="V30">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1020,8 +1107,11 @@
       <c r="D31">
         <v>73.759765625</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="V31">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1034,8 +1124,11 @@
       <c r="D32">
         <v>64.56005859375</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="V32">
+        <v>74.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1047,6 +1140,9 @@
       </c>
       <c r="D33">
         <v>47.860107421875</v>
+      </c>
+      <c r="V33">
+        <v>49.4</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -737,7 +737,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V9">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1125,7 +1125,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="V32">
-        <v>74.25</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1142,7 +1142,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V33">
-        <v>49.4</v>
+        <v>52.8</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -618,7 +618,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="V2">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -635,7 +635,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="V3">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -652,7 +652,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="V4">
-        <v>50.35</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -669,7 +669,7 @@
         <v>70</v>
       </c>
       <c r="V5">
-        <v>63.25</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -686,7 +686,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="V6">
-        <v>38.8</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -703,7 +703,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="V7">
-        <v>35.75</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -720,7 +720,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="V8">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -737,7 +737,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V9">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -754,7 +754,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="V10">
-        <v>62.25</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -771,7 +771,7 @@
         <v>44.260009765625</v>
       </c>
       <c r="V11">
-        <v>46.35</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -788,7 +788,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="V12">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -805,7 +805,7 @@
         <v>84.85986328125</v>
       </c>
       <c r="V13">
-        <v>45.15</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -819,7 +819,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="V14">
-        <v>62.4</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -836,7 +836,7 @@
         <v>74.06005859375</v>
       </c>
       <c r="V15">
-        <v>83.55</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -853,7 +853,7 @@
         <v>54.60009765625</v>
       </c>
       <c r="V16">
-        <v>69.2</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -870,7 +870,7 @@
         <v>84.259765625</v>
       </c>
       <c r="V17">
-        <v>50.3</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -887,7 +887,7 @@
         <v>59.25</v>
       </c>
       <c r="V18">
-        <v>37.8</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -904,7 +904,7 @@
         <v>54.159912109375</v>
       </c>
       <c r="V19">
-        <v>59.95</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -921,7 +921,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="V20">
-        <v>63.55</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -938,7 +938,7 @@
         <v>50.260009765625</v>
       </c>
       <c r="V21">
-        <v>37.55</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -955,7 +955,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="V22">
-        <v>65.40000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -972,7 +972,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="V23">
-        <v>15.7</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1006,7 +1006,7 @@
         <v>64.7001953125</v>
       </c>
       <c r="V25">
-        <v>35.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1023,7 +1023,7 @@
         <v>44.06005859375</v>
       </c>
       <c r="V26">
-        <v>75.05</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -1040,7 +1040,7 @@
         <v>49</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -1057,7 +1057,7 @@
         <v>61.9599609375</v>
       </c>
       <c r="V28">
-        <v>42.5</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -1074,7 +1074,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="V29">
-        <v>26.1</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -1091,7 +1091,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="V30">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -1108,7 +1108,7 @@
         <v>73.759765625</v>
       </c>
       <c r="V31">
-        <v>53.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -1125,7 +1125,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="V32">
-        <v>78.75</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1142,7 +1142,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V33">
-        <v>52.8</v>
+        <v>61.91</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -618,7 +618,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="V2">
-        <v>59.2</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -635,7 +635,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="V3">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -652,7 +652,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="V4">
-        <v>65.15000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -669,7 +669,7 @@
         <v>70</v>
       </c>
       <c r="V5">
-        <v>73.75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -686,7 +686,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="V6">
-        <v>56.91</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -703,7 +703,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="V7">
-        <v>49.15</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -720,7 +720,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="V8">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -737,7 +737,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V9">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -754,7 +754,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="V10">
-        <v>66.25</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -771,7 +771,7 @@
         <v>44.260009765625</v>
       </c>
       <c r="V11">
-        <v>87.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -788,7 +788,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="V12">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -805,7 +805,7 @@
         <v>84.85986328125</v>
       </c>
       <c r="V13">
-        <v>61.95</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -819,7 +819,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="V14">
-        <v>71.51000000000001</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -836,7 +836,7 @@
         <v>74.06005859375</v>
       </c>
       <c r="V15">
-        <v>88.36</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -853,7 +853,7 @@
         <v>54.60009765625</v>
       </c>
       <c r="V16">
-        <v>73.70999999999999</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -870,7 +870,7 @@
         <v>84.259765625</v>
       </c>
       <c r="V17">
-        <v>77.52</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -887,7 +887,7 @@
         <v>59.25</v>
       </c>
       <c r="V18">
-        <v>53.11</v>
+        <v>73.78</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -904,7 +904,7 @@
         <v>54.159912109375</v>
       </c>
       <c r="V19">
-        <v>63.95</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -921,7 +921,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="V20">
-        <v>75.16</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -938,7 +938,7 @@
         <v>50.260009765625</v>
       </c>
       <c r="V21">
-        <v>48.25</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -955,7 +955,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="V22">
-        <v>69.7</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -972,7 +972,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="V23">
-        <v>39.71</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -989,7 +989,7 @@
         <v>57.60009765625</v>
       </c>
       <c r="V24">
-        <v>79.59999999999999</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1006,7 +1006,7 @@
         <v>64.7001953125</v>
       </c>
       <c r="V25">
-        <v>48</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1023,7 +1023,7 @@
         <v>44.06005859375</v>
       </c>
       <c r="V26">
-        <v>74.75</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -1040,7 +1040,7 @@
         <v>49</v>
       </c>
       <c r="V27">
-        <v>40.21</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -1057,7 +1057,7 @@
         <v>61.9599609375</v>
       </c>
       <c r="V28">
-        <v>54.01</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -1074,7 +1074,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="V29">
-        <v>48.01</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -1091,7 +1091,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="V30">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -1108,7 +1108,7 @@
         <v>73.759765625</v>
       </c>
       <c r="V31">
-        <v>58.2</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -1125,7 +1125,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="V32">
-        <v>82.75</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1142,7 +1142,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="V33">
-        <v>61.91</v>
+        <v>81.88</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 2</t>
+    <t>Parcial Rodada 3</t>
   </si>
   <si>
     <t>time_id</t>
@@ -615,10 +615,10 @@
         <v>68.06005859375</v>
       </c>
       <c r="D2">
-        <v>68.06005859375</v>
-      </c>
-      <c r="V2">
-        <v>72.56</v>
+        <v>72.7001953125</v>
+      </c>
+      <c r="E2">
+        <v>72.7001953125</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -632,10 +632,10 @@
         <v>53.659912109375</v>
       </c>
       <c r="D3">
-        <v>53.659912109375</v>
-      </c>
-      <c r="V3">
-        <v>81.48</v>
+        <v>81.47998046875</v>
+      </c>
+      <c r="E3">
+        <v>81.47998046875</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -649,10 +649,10 @@
         <v>66.85986328125</v>
       </c>
       <c r="D4">
-        <v>66.85986328125</v>
-      </c>
-      <c r="V4">
-        <v>92.7</v>
+        <v>92.7001953125</v>
+      </c>
+      <c r="E4">
+        <v>92.7001953125</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -666,9 +666,9 @@
         <v>70</v>
       </c>
       <c r="D5">
-        <v>70</v>
-      </c>
-      <c r="V5">
+        <v>87.5</v>
+      </c>
+      <c r="E5">
         <v>87.5</v>
       </c>
     </row>
@@ -683,10 +683,10 @@
         <v>58.9599609375</v>
       </c>
       <c r="D6">
-        <v>58.9599609375</v>
-      </c>
-      <c r="V6">
-        <v>79.28</v>
+        <v>79.27978515625</v>
+      </c>
+      <c r="E6">
+        <v>79.27978515625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -700,10 +700,10 @@
         <v>57.449951171875</v>
       </c>
       <c r="D7">
-        <v>57.449951171875</v>
-      </c>
-      <c r="V7">
-        <v>83.2</v>
+        <v>83.2001953125</v>
+      </c>
+      <c r="E7">
+        <v>83.2001953125</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -717,10 +717,10 @@
         <v>68.06005859375</v>
       </c>
       <c r="D8">
-        <v>68.06005859375</v>
-      </c>
-      <c r="V8">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
+      </c>
+      <c r="E8">
+        <v>82.18017578125</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -734,10 +734,10 @@
         <v>47.860107421875</v>
       </c>
       <c r="D9">
-        <v>47.860107421875</v>
-      </c>
-      <c r="V9">
-        <v>72.18000000000001</v>
+        <v>72.18017578125</v>
+      </c>
+      <c r="E9">
+        <v>72.18017578125</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -751,10 +751,10 @@
         <v>64.56005859375</v>
       </c>
       <c r="D10">
-        <v>64.56005859375</v>
-      </c>
-      <c r="V10">
-        <v>86.59999999999999</v>
+        <v>86.60009765625</v>
+      </c>
+      <c r="E10">
+        <v>86.60009765625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -768,9 +768,9 @@
         <v>44.260009765625</v>
       </c>
       <c r="D11">
-        <v>44.260009765625</v>
-      </c>
-      <c r="V11">
+        <v>90</v>
+      </c>
+      <c r="E11">
         <v>90</v>
       </c>
     </row>
@@ -785,10 +785,10 @@
         <v>61.56005859375</v>
       </c>
       <c r="D12">
-        <v>61.56005859375</v>
-      </c>
-      <c r="V12">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
+      </c>
+      <c r="E12">
+        <v>82.18017578125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -802,10 +802,10 @@
         <v>84.85986328125</v>
       </c>
       <c r="D13">
-        <v>84.85986328125</v>
-      </c>
-      <c r="V13">
-        <v>79.45</v>
+        <v>79.4501953125</v>
+      </c>
+      <c r="E13">
+        <v>79.4501953125</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -818,9 +818,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>91.48</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -833,10 +830,10 @@
         <v>74.06005859375</v>
       </c>
       <c r="D15">
-        <v>74.06005859375</v>
-      </c>
-      <c r="V15">
-        <v>93.78</v>
+        <v>93.77978515625</v>
+      </c>
+      <c r="E15">
+        <v>93.77978515625</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -850,13 +847,13 @@
         <v>54.60009765625</v>
       </c>
       <c r="D16">
-        <v>54.60009765625</v>
-      </c>
-      <c r="V16">
-        <v>85.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>85.580078125</v>
+      </c>
+      <c r="E16">
+        <v>85.580078125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -867,13 +864,13 @@
         <v>84.259765625</v>
       </c>
       <c r="D17">
-        <v>84.259765625</v>
-      </c>
-      <c r="V17">
-        <v>82.61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>82.60986328125</v>
+      </c>
+      <c r="E17">
+        <v>82.60986328125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -884,13 +881,13 @@
         <v>59.25</v>
       </c>
       <c r="D18">
-        <v>59.25</v>
-      </c>
-      <c r="V18">
-        <v>73.78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>73.77978515625</v>
+      </c>
+      <c r="E18">
+        <v>73.77978515625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -901,13 +898,13 @@
         <v>54.159912109375</v>
       </c>
       <c r="D19">
-        <v>54.159912109375</v>
-      </c>
-      <c r="V19">
-        <v>86.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>86.7001953125</v>
+      </c>
+      <c r="E19">
+        <v>86.7001953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -918,13 +915,13 @@
         <v>63.89990234375</v>
       </c>
       <c r="D20">
-        <v>63.89990234375</v>
-      </c>
-      <c r="V20">
-        <v>92.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>92.77978515625</v>
+      </c>
+      <c r="E20">
+        <v>92.77978515625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -935,13 +932,13 @@
         <v>50.260009765625</v>
       </c>
       <c r="D21">
-        <v>50.260009765625</v>
-      </c>
-      <c r="V21">
-        <v>57.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+        <v>57.550048828125</v>
+      </c>
+      <c r="E21">
+        <v>57.550048828125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -952,13 +949,13 @@
         <v>73.9599609375</v>
       </c>
       <c r="D22">
-        <v>73.9599609375</v>
-      </c>
-      <c r="V22">
-        <v>92.76000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>92.89990234375</v>
+      </c>
+      <c r="E22">
+        <v>92.89990234375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -969,13 +966,13 @@
         <v>72.7001953125</v>
       </c>
       <c r="D23">
-        <v>72.7001953125</v>
-      </c>
-      <c r="V23">
-        <v>64.58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>64.580078125</v>
+      </c>
+      <c r="E23">
+        <v>64.580078125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -986,13 +983,13 @@
         <v>57.60009765625</v>
       </c>
       <c r="D24">
-        <v>57.60009765625</v>
-      </c>
-      <c r="V24">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="E24">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1003,13 +1000,13 @@
         <v>64.7001953125</v>
       </c>
       <c r="D25">
-        <v>64.7001953125</v>
-      </c>
-      <c r="V25">
-        <v>60.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>60.699951171875</v>
+      </c>
+      <c r="E25">
+        <v>60.699951171875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1020,13 +1017,13 @@
         <v>44.06005859375</v>
       </c>
       <c r="D26">
-        <v>44.06005859375</v>
-      </c>
-      <c r="V26">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+        <v>85.7001953125</v>
+      </c>
+      <c r="E26">
+        <v>85.7001953125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1037,13 +1034,10 @@
         <v>49</v>
       </c>
       <c r="D27">
-        <v>49</v>
-      </c>
-      <c r="V27">
-        <v>36.43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+        <v>36.429931640625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1054,13 +1048,13 @@
         <v>61.9599609375</v>
       </c>
       <c r="D28">
-        <v>61.9599609375</v>
-      </c>
-      <c r="V28">
-        <v>84.48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>84.47998046875</v>
+      </c>
+      <c r="E28">
+        <v>84.47998046875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1071,13 +1065,13 @@
         <v>60.159912109375</v>
       </c>
       <c r="D29">
-        <v>60.159912109375</v>
-      </c>
-      <c r="V29">
-        <v>64.58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>64.580078125</v>
+      </c>
+      <c r="E29">
+        <v>64.580078125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1088,13 +1082,13 @@
         <v>62.56005859375</v>
       </c>
       <c r="D30">
-        <v>62.56005859375</v>
-      </c>
-      <c r="V30">
-        <v>96.48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>96.47998046875</v>
+      </c>
+      <c r="E30">
+        <v>96.47998046875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1105,13 +1099,13 @@
         <v>73.759765625</v>
       </c>
       <c r="D31">
-        <v>73.759765625</v>
-      </c>
-      <c r="V31">
-        <v>81.26000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>81.39990234375</v>
+      </c>
+      <c r="E31">
+        <v>81.39990234375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1122,13 +1116,13 @@
         <v>64.56005859375</v>
       </c>
       <c r="D32">
-        <v>64.56005859375</v>
-      </c>
-      <c r="V32">
         <v>105.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="E32">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1139,10 +1133,10 @@
         <v>47.860107421875</v>
       </c>
       <c r="D33">
-        <v>47.860107421875</v>
-      </c>
-      <c r="V33">
-        <v>81.88</v>
+        <v>81.8798828125</v>
+      </c>
+      <c r="E33">
+        <v>81.8798828125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -620,6 +620,9 @@
       <c r="E2">
         <v>72.7001953125</v>
       </c>
+      <c r="V2">
+        <v>38.07</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -637,6 +640,9 @@
       <c r="E3">
         <v>81.47998046875</v>
       </c>
+      <c r="V3">
+        <v>38.07</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -654,6 +660,9 @@
       <c r="E4">
         <v>92.7001953125</v>
       </c>
+      <c r="V4">
+        <v>55.19</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -671,6 +680,9 @@
       <c r="E5">
         <v>87.5</v>
       </c>
+      <c r="V5">
+        <v>49.27</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -688,6 +700,9 @@
       <c r="E6">
         <v>79.27978515625</v>
       </c>
+      <c r="V6">
+        <v>45.77</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -705,6 +720,9 @@
       <c r="E7">
         <v>83.2001953125</v>
       </c>
+      <c r="V7">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -722,6 +740,9 @@
       <c r="E8">
         <v>82.18017578125</v>
       </c>
+      <c r="V8">
+        <v>45.17</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -739,6 +760,9 @@
       <c r="E9">
         <v>72.18017578125</v>
       </c>
+      <c r="V9">
+        <v>62.8</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -756,6 +780,9 @@
       <c r="E10">
         <v>86.60009765625</v>
       </c>
+      <c r="V10">
+        <v>50.07</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -773,6 +800,9 @@
       <c r="E11">
         <v>90</v>
       </c>
+      <c r="V11">
+        <v>42.47</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -790,6 +820,9 @@
       <c r="E12">
         <v>82.18017578125</v>
       </c>
+      <c r="V12">
+        <v>45.17</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -807,6 +840,9 @@
       <c r="E13">
         <v>79.4501953125</v>
       </c>
+      <c r="V13">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -818,6 +854,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>58.47</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -835,6 +874,9 @@
       <c r="E15">
         <v>93.77978515625</v>
       </c>
+      <c r="V15">
+        <v>54.97</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -852,8 +894,11 @@
       <c r="E16">
         <v>85.580078125</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="V16">
+        <v>58.37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -869,8 +914,11 @@
       <c r="E17">
         <v>82.60986328125</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="V17">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -886,8 +934,11 @@
       <c r="E18">
         <v>73.77978515625</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="V18">
+        <v>54.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -903,8 +954,11 @@
       <c r="E19">
         <v>86.7001953125</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="V19">
+        <v>59.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -920,8 +974,11 @@
       <c r="E20">
         <v>92.77978515625</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="V20">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -937,8 +994,11 @@
       <c r="E21">
         <v>57.550048828125</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="V21">
+        <v>28.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -954,8 +1014,11 @@
       <c r="E22">
         <v>92.89990234375</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="V22">
+        <v>47.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -971,8 +1034,11 @@
       <c r="E23">
         <v>64.580078125</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="V23">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -988,8 +1054,11 @@
       <c r="E24">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="V24">
+        <v>39.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1005,8 +1074,11 @@
       <c r="E25">
         <v>60.699951171875</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="V25">
+        <v>40.17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1022,8 +1094,11 @@
       <c r="E26">
         <v>85.7001953125</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="V26">
+        <v>41.57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1036,8 +1111,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="V27">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1053,8 +1131,11 @@
       <c r="E28">
         <v>84.47998046875</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="V28">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1070,8 +1151,11 @@
       <c r="E29">
         <v>64.580078125</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="V29">
+        <v>57.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1087,8 +1171,11 @@
       <c r="E30">
         <v>96.47998046875</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="V30">
+        <v>53.77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1104,8 +1191,11 @@
       <c r="E31">
         <v>81.39990234375</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="V31">
+        <v>40.57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1121,8 +1211,11 @@
       <c r="E32">
         <v>105.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="V32">
+        <v>50.77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1137,6 +1230,9 @@
       </c>
       <c r="E33">
         <v>81.8798828125</v>
+      </c>
+      <c r="V33">
+        <v>69.27</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -621,7 +621,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="V2">
-        <v>38.07</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -641,7 +641,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="V3">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -661,7 +661,7 @@
         <v>92.7001953125</v>
       </c>
       <c r="V4">
-        <v>55.19</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -681,7 +681,7 @@
         <v>87.5</v>
       </c>
       <c r="V5">
-        <v>49.27</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -701,7 +701,7 @@
         <v>79.27978515625</v>
       </c>
       <c r="V6">
-        <v>45.77</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -721,7 +721,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="V7">
-        <v>27.9</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -741,7 +741,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="V8">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -761,7 +761,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="V9">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -781,7 +781,7 @@
         <v>86.60009765625</v>
       </c>
       <c r="V10">
-        <v>50.07</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -801,7 +801,7 @@
         <v>90</v>
       </c>
       <c r="V11">
-        <v>42.47</v>
+        <v>68.26000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -821,7 +821,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="V12">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -841,7 +841,7 @@
         <v>79.4501953125</v>
       </c>
       <c r="V13">
-        <v>21.6</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -855,7 +855,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="V14">
-        <v>58.47</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -875,7 +875,7 @@
         <v>93.77978515625</v>
       </c>
       <c r="V15">
-        <v>54.97</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -895,7 +895,7 @@
         <v>85.580078125</v>
       </c>
       <c r="V16">
-        <v>58.37</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -915,7 +915,7 @@
         <v>82.60986328125</v>
       </c>
       <c r="V17">
-        <v>29.2</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -935,7 +935,7 @@
         <v>73.77978515625</v>
       </c>
       <c r="V18">
-        <v>54.27</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -955,7 +955,7 @@
         <v>86.7001953125</v>
       </c>
       <c r="V19">
-        <v>59.87</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -975,7 +975,7 @@
         <v>92.77978515625</v>
       </c>
       <c r="V20">
-        <v>40.6</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -995,7 +995,7 @@
         <v>57.550048828125</v>
       </c>
       <c r="V21">
-        <v>28.49</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -1015,7 +1015,7 @@
         <v>92.89990234375</v>
       </c>
       <c r="V22">
-        <v>47.57</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -1035,7 +1035,7 @@
         <v>64.580078125</v>
       </c>
       <c r="V23">
-        <v>58.4</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1055,7 +1055,7 @@
         <v>84.5</v>
       </c>
       <c r="V24">
-        <v>39.87</v>
+        <v>78.86</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1075,7 +1075,7 @@
         <v>60.699951171875</v>
       </c>
       <c r="V25">
-        <v>40.17</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1095,7 +1095,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="V26">
-        <v>41.57</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -1112,7 +1112,7 @@
         <v>36.429931640625</v>
       </c>
       <c r="V27">
-        <v>17.5</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -1132,7 +1132,7 @@
         <v>84.47998046875</v>
       </c>
       <c r="V28">
-        <v>35.5</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -1152,7 +1152,7 @@
         <v>64.580078125</v>
       </c>
       <c r="V29">
-        <v>57.47</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -1172,7 +1172,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="V30">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -1192,7 +1192,7 @@
         <v>81.39990234375</v>
       </c>
       <c r="V31">
-        <v>40.57</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -1212,7 +1212,7 @@
         <v>105.5</v>
       </c>
       <c r="V32">
-        <v>50.77</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1232,7 +1232,7 @@
         <v>81.8798828125</v>
       </c>
       <c r="V33">
-        <v>69.27</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 3</t>
+    <t>Parcial Rodada 4</t>
   </si>
   <si>
     <t>time_id</t>
@@ -618,10 +618,10 @@
         <v>72.7001953125</v>
       </c>
       <c r="E2">
-        <v>72.7001953125</v>
-      </c>
-      <c r="V2">
-        <v>79.06</v>
+        <v>79.85986328125</v>
+      </c>
+      <c r="F2">
+        <v>79.85986328125</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -638,10 +638,10 @@
         <v>81.47998046875</v>
       </c>
       <c r="E3">
-        <v>81.47998046875</v>
-      </c>
-      <c r="V3">
-        <v>78.45999999999999</v>
+        <v>79.259765625</v>
+      </c>
+      <c r="F3">
+        <v>79.259765625</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -658,10 +658,10 @@
         <v>92.7001953125</v>
       </c>
       <c r="E4">
-        <v>92.7001953125</v>
-      </c>
-      <c r="V4">
-        <v>73.23999999999999</v>
+        <v>72.740234375</v>
+      </c>
+      <c r="F4">
+        <v>72.740234375</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -678,10 +678,10 @@
         <v>87.5</v>
       </c>
       <c r="E5">
-        <v>87.5</v>
-      </c>
-      <c r="V5">
-        <v>88.06</v>
+        <v>88.06005859375</v>
+      </c>
+      <c r="F5">
+        <v>88.06005859375</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -698,10 +698,10 @@
         <v>79.27978515625</v>
       </c>
       <c r="E6">
-        <v>79.27978515625</v>
-      </c>
-      <c r="V6">
-        <v>86.66</v>
+        <v>86.66015625</v>
+      </c>
+      <c r="F6">
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -718,10 +718,10 @@
         <v>83.2001953125</v>
       </c>
       <c r="E7">
-        <v>83.2001953125</v>
-      </c>
-      <c r="V7">
-        <v>70.8</v>
+        <v>70.7998046875</v>
+      </c>
+      <c r="F7">
+        <v>70.7998046875</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -738,10 +738,10 @@
         <v>82.18017578125</v>
       </c>
       <c r="E8">
-        <v>82.18017578125</v>
-      </c>
-      <c r="V8">
-        <v>105.76</v>
+        <v>105.759765625</v>
+      </c>
+      <c r="F8">
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -758,10 +758,10 @@
         <v>72.18017578125</v>
       </c>
       <c r="E9">
-        <v>72.18017578125</v>
-      </c>
-      <c r="V9">
-        <v>97.40000000000001</v>
+        <v>97.39990234375</v>
+      </c>
+      <c r="F9">
+        <v>97.39990234375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -778,10 +778,10 @@
         <v>86.60009765625</v>
       </c>
       <c r="E10">
-        <v>86.60009765625</v>
-      </c>
-      <c r="V10">
-        <v>69.66</v>
+        <v>70.35986328125</v>
+      </c>
+      <c r="F10">
+        <v>70.35986328125</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -798,10 +798,10 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>90</v>
-      </c>
-      <c r="V11">
-        <v>68.26000000000001</v>
+        <v>68.9599609375</v>
+      </c>
+      <c r="F11">
+        <v>68.9599609375</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -818,10 +818,10 @@
         <v>82.18017578125</v>
       </c>
       <c r="E12">
-        <v>82.18017578125</v>
-      </c>
-      <c r="V12">
-        <v>105.76</v>
+        <v>105.759765625</v>
+      </c>
+      <c r="F12">
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -838,10 +838,10 @@
         <v>79.4501953125</v>
       </c>
       <c r="E13">
-        <v>79.4501953125</v>
-      </c>
-      <c r="V13">
-        <v>79.76000000000001</v>
+        <v>78.93994140625</v>
+      </c>
+      <c r="F13">
+        <v>78.93994140625</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -854,9 +854,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>98.56</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -872,10 +869,10 @@
         <v>93.77978515625</v>
       </c>
       <c r="E15">
-        <v>93.77978515625</v>
-      </c>
-      <c r="V15">
-        <v>93.45999999999999</v>
+        <v>94.259765625</v>
+      </c>
+      <c r="F15">
+        <v>94.259765625</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -892,13 +889,13 @@
         <v>85.580078125</v>
       </c>
       <c r="E16">
-        <v>85.580078125</v>
-      </c>
-      <c r="V16">
-        <v>66.95999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>67.759765625</v>
+      </c>
+      <c r="F16">
+        <v>67.759765625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -912,13 +909,13 @@
         <v>82.60986328125</v>
       </c>
       <c r="E17">
-        <v>82.60986328125</v>
-      </c>
-      <c r="V17">
         <v>81.25</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="F17">
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -932,13 +929,13 @@
         <v>73.77978515625</v>
       </c>
       <c r="E18">
-        <v>73.77978515625</v>
-      </c>
-      <c r="V18">
-        <v>92.95999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>93.759765625</v>
+      </c>
+      <c r="F18">
+        <v>93.759765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -952,13 +949,13 @@
         <v>86.7001953125</v>
       </c>
       <c r="E19">
-        <v>86.7001953125</v>
-      </c>
-      <c r="V19">
-        <v>74.76000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>75.56005859375</v>
+      </c>
+      <c r="F19">
+        <v>75.56005859375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -972,13 +969,13 @@
         <v>92.77978515625</v>
       </c>
       <c r="E20">
-        <v>92.77978515625</v>
-      </c>
-      <c r="V20">
-        <v>78.40000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>78.39990234375</v>
+      </c>
+      <c r="F20">
+        <v>78.39990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -992,13 +989,13 @@
         <v>57.550048828125</v>
       </c>
       <c r="E21">
-        <v>57.550048828125</v>
-      </c>
-      <c r="V21">
-        <v>70.04000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+        <v>70.83984375</v>
+      </c>
+      <c r="F21">
+        <v>70.83984375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1012,13 +1009,13 @@
         <v>92.89990234375</v>
       </c>
       <c r="E22">
-        <v>92.89990234375</v>
-      </c>
-      <c r="V22">
-        <v>81.76000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>81.759765625</v>
+      </c>
+      <c r="F22">
+        <v>81.759765625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1032,13 +1029,13 @@
         <v>64.580078125</v>
       </c>
       <c r="E23">
-        <v>64.580078125</v>
-      </c>
-      <c r="V23">
-        <v>98.65000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>98.64990234375</v>
+      </c>
+      <c r="F23">
+        <v>98.64990234375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1052,13 +1049,13 @@
         <v>84.5</v>
       </c>
       <c r="E24">
-        <v>84.5</v>
-      </c>
-      <c r="V24">
-        <v>78.86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>78.85986328125</v>
+      </c>
+      <c r="F24">
+        <v>78.85986328125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1072,13 +1069,13 @@
         <v>60.699951171875</v>
       </c>
       <c r="E25">
-        <v>60.699951171875</v>
-      </c>
-      <c r="V25">
-        <v>86.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>86.16015625</v>
+      </c>
+      <c r="F25">
+        <v>86.16015625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1092,13 +1089,10 @@
         <v>85.7001953125</v>
       </c>
       <c r="E26">
-        <v>85.7001953125</v>
-      </c>
-      <c r="V26">
-        <v>64.45999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+        <v>65.259765625</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1111,11 +1105,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>51.65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1129,13 +1120,13 @@
         <v>84.47998046875</v>
       </c>
       <c r="E28">
-        <v>84.47998046875</v>
-      </c>
-      <c r="V28">
-        <v>87.40000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>87.39990234375</v>
+      </c>
+      <c r="F28">
+        <v>87.39990234375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1149,13 +1140,13 @@
         <v>64.580078125</v>
       </c>
       <c r="E29">
-        <v>64.580078125</v>
-      </c>
-      <c r="V29">
-        <v>88.76000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>88.759765625</v>
+      </c>
+      <c r="F29">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1169,13 +1160,13 @@
         <v>96.47998046875</v>
       </c>
       <c r="E30">
-        <v>96.47998046875</v>
-      </c>
-      <c r="V30">
-        <v>87.45999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>87.4599609375</v>
+      </c>
+      <c r="F30">
+        <v>87.4599609375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1189,13 +1180,13 @@
         <v>81.39990234375</v>
       </c>
       <c r="E31">
-        <v>81.39990234375</v>
-      </c>
-      <c r="V31">
-        <v>80.56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>81.35986328125</v>
+      </c>
+      <c r="F31">
+        <v>81.35986328125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1209,13 +1200,13 @@
         <v>105.5</v>
       </c>
       <c r="E32">
-        <v>105.5</v>
-      </c>
-      <c r="V32">
-        <v>80.36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>81.16015625</v>
+      </c>
+      <c r="F32">
+        <v>81.16015625</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1229,10 +1220,10 @@
         <v>81.8798828125</v>
       </c>
       <c r="E33">
-        <v>81.8798828125</v>
-      </c>
-      <c r="V33">
-        <v>97.76000000000001</v>
+        <v>97.759765625</v>
+      </c>
+      <c r="F33">
+        <v>97.759765625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -623,6 +623,9 @@
       <c r="F2">
         <v>79.85986328125</v>
       </c>
+      <c r="V2">
+        <v>32.73</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -643,6 +646,9 @@
       <c r="F3">
         <v>79.259765625</v>
       </c>
+      <c r="V3">
+        <v>59.53</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -663,6 +669,9 @@
       <c r="F4">
         <v>72.740234375</v>
       </c>
+      <c r="V4">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -683,6 +692,9 @@
       <c r="F5">
         <v>88.06005859375</v>
       </c>
+      <c r="V5">
+        <v>28.85</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -703,6 +715,9 @@
       <c r="F6">
         <v>86.66015625</v>
       </c>
+      <c r="V6">
+        <v>70.40000000000001</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -723,6 +738,9 @@
       <c r="F7">
         <v>70.7998046875</v>
       </c>
+      <c r="V7">
+        <v>51.19</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -743,6 +761,9 @@
       <c r="F8">
         <v>105.759765625</v>
       </c>
+      <c r="V8">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -763,6 +784,9 @@
       <c r="F9">
         <v>97.39990234375</v>
       </c>
+      <c r="V9">
+        <v>65.55</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -783,6 +807,9 @@
       <c r="F10">
         <v>70.35986328125</v>
       </c>
+      <c r="V10">
+        <v>32.3</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -803,6 +830,9 @@
       <c r="F11">
         <v>68.9599609375</v>
       </c>
+      <c r="V11">
+        <v>23.9</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -823,6 +853,9 @@
       <c r="F12">
         <v>105.759765625</v>
       </c>
+      <c r="V12">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -843,6 +876,9 @@
       <c r="F13">
         <v>78.93994140625</v>
       </c>
+      <c r="V13">
+        <v>31.78</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -854,6 +890,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>41.55</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -874,6 +913,9 @@
       <c r="F15">
         <v>94.259765625</v>
       </c>
+      <c r="V15">
+        <v>46.55</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -894,8 +936,11 @@
       <c r="F16">
         <v>67.759765625</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="V16">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -914,8 +959,11 @@
       <c r="F17">
         <v>81.25</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="V17">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -934,8 +982,11 @@
       <c r="F18">
         <v>93.759765625</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="V18">
+        <v>44.07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -954,8 +1005,11 @@
       <c r="F19">
         <v>75.56005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="V19">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -974,8 +1028,11 @@
       <c r="F20">
         <v>78.39990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="V20">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -994,8 +1051,11 @@
       <c r="F21">
         <v>70.83984375</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="V21">
+        <v>28.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1014,8 +1074,11 @@
       <c r="F22">
         <v>81.759765625</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="V22">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1034,8 +1097,11 @@
       <c r="F23">
         <v>98.64990234375</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="V23">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1054,8 +1120,11 @@
       <c r="F24">
         <v>78.85986328125</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="V24">
+        <v>73.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1074,8 +1143,11 @@
       <c r="F25">
         <v>86.16015625</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="V25">
+        <v>47.45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1091,8 +1163,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="V26">
+        <v>34.05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1105,8 +1180,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="V27">
+        <v>21.65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1125,8 +1203,11 @@
       <c r="F28">
         <v>87.39990234375</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="V28">
+        <v>45.35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1145,8 +1226,11 @@
       <c r="F29">
         <v>88.759765625</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="V29">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1165,8 +1249,11 @@
       <c r="F30">
         <v>87.4599609375</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="V30">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1185,8 +1272,11 @@
       <c r="F31">
         <v>81.35986328125</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="V31">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1205,8 +1295,11 @@
       <c r="F32">
         <v>81.16015625</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="V32">
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1224,6 +1317,9 @@
       </c>
       <c r="F33">
         <v>97.759765625</v>
+      </c>
+      <c r="V33">
+        <v>65.55</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -624,7 +624,7 @@
         <v>79.85986328125</v>
       </c>
       <c r="V2">
-        <v>32.73</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -647,7 +647,7 @@
         <v>79.259765625</v>
       </c>
       <c r="V3">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -670,7 +670,7 @@
         <v>72.740234375</v>
       </c>
       <c r="V4">
-        <v>48.89</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -693,7 +693,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="V5">
-        <v>28.85</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -716,7 +716,7 @@
         <v>86.66015625</v>
       </c>
       <c r="V6">
-        <v>70.40000000000001</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -739,7 +739,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="V7">
-        <v>51.19</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -762,7 +762,7 @@
         <v>105.759765625</v>
       </c>
       <c r="V8">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -785,7 +785,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="V9">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -808,7 +808,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="V10">
-        <v>32.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -831,7 +831,7 @@
         <v>68.9599609375</v>
       </c>
       <c r="V11">
-        <v>23.9</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -854,7 +854,7 @@
         <v>105.759765625</v>
       </c>
       <c r="V12">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -877,7 +877,7 @@
         <v>78.93994140625</v>
       </c>
       <c r="V13">
-        <v>31.78</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -891,7 +891,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="V14">
-        <v>41.55</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -914,7 +914,7 @@
         <v>94.259765625</v>
       </c>
       <c r="V15">
-        <v>46.55</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -937,7 +937,7 @@
         <v>67.759765625</v>
       </c>
       <c r="V16">
-        <v>35.7</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -960,7 +960,7 @@
         <v>81.25</v>
       </c>
       <c r="V17">
-        <v>18.4</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -983,7 +983,7 @@
         <v>93.759765625</v>
       </c>
       <c r="V18">
-        <v>44.07</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1006,7 +1006,7 @@
         <v>75.56005859375</v>
       </c>
       <c r="V19">
-        <v>34.9</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1029,7 +1029,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="V20">
-        <v>51.7</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1052,7 +1052,7 @@
         <v>70.83984375</v>
       </c>
       <c r="V21">
-        <v>28.33</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -1075,7 +1075,7 @@
         <v>81.759765625</v>
       </c>
       <c r="V22">
-        <v>25.3</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -1098,7 +1098,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="V23">
-        <v>42.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1121,7 +1121,7 @@
         <v>78.85986328125</v>
       </c>
       <c r="V24">
-        <v>73.83</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1144,7 +1144,7 @@
         <v>86.16015625</v>
       </c>
       <c r="V25">
-        <v>47.45</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1181,7 +1181,7 @@
         <v>36.429931640625</v>
       </c>
       <c r="V27">
-        <v>21.65</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -1204,7 +1204,7 @@
         <v>87.39990234375</v>
       </c>
       <c r="V28">
-        <v>45.35</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -1227,7 +1227,7 @@
         <v>88.759765625</v>
       </c>
       <c r="V29">
-        <v>58.2</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -1250,7 +1250,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="V30">
-        <v>44.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -1273,7 +1273,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="V31">
-        <v>41.5</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -1296,7 +1296,7 @@
         <v>81.16015625</v>
       </c>
       <c r="V32">
-        <v>47.25</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1319,7 +1319,7 @@
         <v>97.759765625</v>
       </c>
       <c r="V33">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -624,7 +624,7 @@
         <v>79.85986328125</v>
       </c>
       <c r="V2">
-        <v>37.08</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -647,7 +647,7 @@
         <v>79.259765625</v>
       </c>
       <c r="V3">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -670,7 +670,7 @@
         <v>72.740234375</v>
       </c>
       <c r="V4">
-        <v>45.94</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -693,7 +693,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="V5">
-        <v>32.9</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -716,7 +716,7 @@
         <v>86.66015625</v>
       </c>
       <c r="V6">
-        <v>78.66</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -739,7 +739,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="V7">
-        <v>67.26000000000001</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -762,7 +762,7 @@
         <v>105.759765625</v>
       </c>
       <c r="V8">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -808,7 +808,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="V10">
-        <v>35.6</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -831,7 +831,7 @@
         <v>68.9599609375</v>
       </c>
       <c r="V11">
-        <v>37.3</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -854,7 +854,7 @@
         <v>105.759765625</v>
       </c>
       <c r="V12">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -877,7 +877,7 @@
         <v>78.93994140625</v>
       </c>
       <c r="V13">
-        <v>44.63</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -891,7 +891,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="V14">
-        <v>45.75</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -914,7 +914,7 @@
         <v>94.259765625</v>
       </c>
       <c r="V15">
-        <v>55.75</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -937,7 +937,7 @@
         <v>67.759765625</v>
       </c>
       <c r="V16">
-        <v>40.05</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -960,7 +960,7 @@
         <v>81.25</v>
       </c>
       <c r="V17">
-        <v>22.15</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -983,7 +983,7 @@
         <v>93.759765625</v>
       </c>
       <c r="V18">
-        <v>47.58</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1006,7 +1006,7 @@
         <v>75.56005859375</v>
       </c>
       <c r="V19">
-        <v>62.15</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1029,7 +1029,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="V20">
-        <v>64.05</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1075,7 +1075,7 @@
         <v>81.759765625</v>
       </c>
       <c r="V22">
-        <v>31.15</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -1098,7 +1098,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="V23">
-        <v>38.5</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1144,7 +1144,7 @@
         <v>86.16015625</v>
       </c>
       <c r="V25">
-        <v>61.96</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1164,7 +1164,7 @@
         <v>65.259765625</v>
       </c>
       <c r="V26">
-        <v>34.05</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -1181,7 +1181,7 @@
         <v>36.429931640625</v>
       </c>
       <c r="V27">
-        <v>24.25</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -1227,7 +1227,7 @@
         <v>88.759765625</v>
       </c>
       <c r="V29">
-        <v>92.05</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -1250,7 +1250,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="V30">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -1273,7 +1273,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="V31">
-        <v>45.85</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -1296,7 +1296,7 @@
         <v>81.16015625</v>
       </c>
       <c r="V32">
-        <v>47.55</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="33" spans="1:22">

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 4</t>
+    <t>Parcial Rodada 5</t>
   </si>
   <si>
     <t>time_id</t>
@@ -621,10 +621,10 @@
         <v>79.85986328125</v>
       </c>
       <c r="F2">
-        <v>79.85986328125</v>
-      </c>
-      <c r="V2">
-        <v>58.68</v>
+        <v>58.679931640625</v>
+      </c>
+      <c r="G2">
+        <v>58.679931640625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -644,10 +644,10 @@
         <v>79.259765625</v>
       </c>
       <c r="F3">
-        <v>79.259765625</v>
-      </c>
-      <c r="V3">
-        <v>86.43000000000001</v>
+        <v>86.43017578125</v>
+      </c>
+      <c r="G3">
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -667,10 +667,10 @@
         <v>72.740234375</v>
       </c>
       <c r="F4">
-        <v>72.740234375</v>
-      </c>
-      <c r="V4">
-        <v>50.59</v>
+        <v>50.590087890625</v>
+      </c>
+      <c r="G4">
+        <v>50.590087890625</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -690,10 +690,10 @@
         <v>88.06005859375</v>
       </c>
       <c r="F5">
-        <v>88.06005859375</v>
-      </c>
-      <c r="V5">
-        <v>58.53</v>
+        <v>58.530029296875</v>
+      </c>
+      <c r="G5">
+        <v>58.530029296875</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -713,10 +713,10 @@
         <v>86.66015625</v>
       </c>
       <c r="F6">
-        <v>86.66015625</v>
-      </c>
-      <c r="V6">
-        <v>80.36</v>
+        <v>80.35986328125</v>
+      </c>
+      <c r="G6">
+        <v>80.35986328125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -736,10 +736,10 @@
         <v>70.7998046875</v>
       </c>
       <c r="F7">
-        <v>70.7998046875</v>
-      </c>
-      <c r="V7">
-        <v>77.26000000000001</v>
+        <v>77.259765625</v>
+      </c>
+      <c r="G7">
+        <v>77.259765625</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -759,10 +759,10 @@
         <v>105.759765625</v>
       </c>
       <c r="F8">
-        <v>105.759765625</v>
-      </c>
-      <c r="V8">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
+      </c>
+      <c r="G8">
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -782,10 +782,10 @@
         <v>97.39990234375</v>
       </c>
       <c r="F9">
-        <v>97.39990234375</v>
-      </c>
-      <c r="V9">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
+      </c>
+      <c r="G9">
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -805,10 +805,10 @@
         <v>70.35986328125</v>
       </c>
       <c r="F10">
-        <v>70.35986328125</v>
-      </c>
-      <c r="V10">
-        <v>34.9</v>
+        <v>34.89990234375</v>
+      </c>
+      <c r="G10">
+        <v>34.89990234375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -828,10 +828,10 @@
         <v>68.9599609375</v>
       </c>
       <c r="F11">
-        <v>68.9599609375</v>
-      </c>
-      <c r="V11">
-        <v>73.23</v>
+        <v>73.22998046875</v>
+      </c>
+      <c r="G11">
+        <v>73.22998046875</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -851,10 +851,10 @@
         <v>105.759765625</v>
       </c>
       <c r="F12">
-        <v>105.759765625</v>
-      </c>
-      <c r="V12">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
+      </c>
+      <c r="G12">
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -874,10 +874,10 @@
         <v>78.93994140625</v>
       </c>
       <c r="F13">
-        <v>78.93994140625</v>
-      </c>
-      <c r="V13">
-        <v>47.73</v>
+        <v>47.72998046875</v>
+      </c>
+      <c r="G13">
+        <v>47.72998046875</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -890,9 +890,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>74.55</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -911,10 +908,10 @@
         <v>94.259765625</v>
       </c>
       <c r="F15">
-        <v>94.259765625</v>
-      </c>
-      <c r="V15">
-        <v>74.95</v>
+        <v>74.9501953125</v>
+      </c>
+      <c r="G15">
+        <v>74.9501953125</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -934,13 +931,13 @@
         <v>67.759765625</v>
       </c>
       <c r="F16">
-        <v>67.759765625</v>
-      </c>
-      <c r="V16">
         <v>52.25</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="G16">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -957,13 +954,13 @@
         <v>81.25</v>
       </c>
       <c r="F17">
-        <v>81.25</v>
-      </c>
-      <c r="V17">
-        <v>45.65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>45.64990234375</v>
+      </c>
+      <c r="G17">
+        <v>45.64990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -980,13 +977,13 @@
         <v>93.759765625</v>
       </c>
       <c r="F18">
-        <v>93.759765625</v>
-      </c>
-      <c r="V18">
-        <v>51.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>51.929931640625</v>
+      </c>
+      <c r="G18">
+        <v>51.929931640625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1003,13 +1000,13 @@
         <v>75.56005859375</v>
       </c>
       <c r="F19">
-        <v>75.56005859375</v>
-      </c>
-      <c r="V19">
-        <v>82.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>82.0498046875</v>
+      </c>
+      <c r="G19">
+        <v>82.0498046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1026,13 +1023,13 @@
         <v>78.39990234375</v>
       </c>
       <c r="F20">
-        <v>78.39990234375</v>
-      </c>
-      <c r="V20">
-        <v>87.65000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>87.64990234375</v>
+      </c>
+      <c r="G20">
+        <v>87.64990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1049,13 +1046,10 @@
         <v>70.83984375</v>
       </c>
       <c r="F21">
-        <v>70.83984375</v>
-      </c>
-      <c r="V21">
-        <v>27.43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+        <v>27.4300537109375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1072,13 +1066,13 @@
         <v>81.759765625</v>
       </c>
       <c r="F22">
-        <v>81.759765625</v>
-      </c>
-      <c r="V22">
         <v>53.25</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="G22">
+        <v>53.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1095,13 +1089,13 @@
         <v>98.64990234375</v>
       </c>
       <c r="F23">
-        <v>98.64990234375</v>
-      </c>
-      <c r="V23">
-        <v>85.48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>85.47998046875</v>
+      </c>
+      <c r="G23">
+        <v>85.47998046875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1118,13 +1112,13 @@
         <v>78.85986328125</v>
       </c>
       <c r="F24">
-        <v>78.85986328125</v>
-      </c>
-      <c r="V24">
-        <v>85.98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>85.97998046875</v>
+      </c>
+      <c r="G24">
+        <v>85.97998046875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1141,13 +1135,13 @@
         <v>86.16015625</v>
       </c>
       <c r="F25">
-        <v>86.16015625</v>
-      </c>
-      <c r="V25">
-        <v>61.26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>61.260009765625</v>
+      </c>
+      <c r="G25">
+        <v>61.260009765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1163,11 +1157,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>74.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1180,11 +1171,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>29.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1201,13 +1189,13 @@
         <v>87.39990234375</v>
       </c>
       <c r="F28">
-        <v>87.39990234375</v>
-      </c>
-      <c r="V28">
-        <v>53.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>53.14990234375</v>
+      </c>
+      <c r="G28">
+        <v>53.14990234375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1224,13 +1212,13 @@
         <v>88.759765625</v>
       </c>
       <c r="F29">
-        <v>88.759765625</v>
-      </c>
-      <c r="V29">
         <v>109.75</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="G29">
+        <v>109.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1247,13 +1235,13 @@
         <v>87.4599609375</v>
       </c>
       <c r="F30">
-        <v>87.4599609375</v>
-      </c>
-      <c r="V30">
-        <v>81.43000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>81.43017578125</v>
+      </c>
+      <c r="G30">
+        <v>81.43017578125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1270,13 +1258,13 @@
         <v>81.35986328125</v>
       </c>
       <c r="F31">
-        <v>81.35986328125</v>
-      </c>
-      <c r="V31">
-        <v>65.05</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>65.0498046875</v>
+      </c>
+      <c r="G31">
+        <v>65.0498046875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1293,13 +1281,13 @@
         <v>81.16015625</v>
       </c>
       <c r="F32">
-        <v>81.16015625</v>
-      </c>
-      <c r="V32">
         <v>66.75</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="G32">
+        <v>66.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1316,10 +1304,10 @@
         <v>97.759765625</v>
       </c>
       <c r="F33">
-        <v>97.759765625</v>
-      </c>
-      <c r="V33">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
+      </c>
+      <c r="G33">
+        <v>81.64990234375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -626,6 +626,9 @@
       <c r="G2">
         <v>58.679931640625</v>
       </c>
+      <c r="V2">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -649,6 +652,9 @@
       <c r="G3">
         <v>86.43017578125</v>
       </c>
+      <c r="V3">
+        <v>25.7</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -672,6 +678,9 @@
       <c r="G4">
         <v>50.590087890625</v>
       </c>
+      <c r="V4">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -695,6 +704,9 @@
       <c r="G5">
         <v>58.530029296875</v>
       </c>
+      <c r="V5">
+        <v>26.2</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -718,6 +730,9 @@
       <c r="G6">
         <v>80.35986328125</v>
       </c>
+      <c r="V6">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -741,6 +756,9 @@
       <c r="G7">
         <v>77.259765625</v>
       </c>
+      <c r="V7">
+        <v>20.17</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -764,6 +782,9 @@
       <c r="G8">
         <v>65.14990234375</v>
       </c>
+      <c r="V8">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -787,6 +808,9 @@
       <c r="G9">
         <v>81.64990234375</v>
       </c>
+      <c r="V9">
+        <v>13.8</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -810,6 +834,9 @@
       <c r="G10">
         <v>34.89990234375</v>
       </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -833,6 +860,9 @@
       <c r="G11">
         <v>73.22998046875</v>
       </c>
+      <c r="V11">
+        <v>16.59</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -856,6 +886,9 @@
       <c r="G12">
         <v>65.14990234375</v>
       </c>
+      <c r="V12">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -879,6 +912,9 @@
       <c r="G13">
         <v>47.72998046875</v>
       </c>
+      <c r="V13">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -890,6 +926,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -913,6 +952,9 @@
       <c r="G15">
         <v>74.9501953125</v>
       </c>
+      <c r="V15">
+        <v>41.6</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -936,8 +978,11 @@
       <c r="G16">
         <v>52.25</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="V16">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -959,8 +1004,11 @@
       <c r="G17">
         <v>45.64990234375</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="V17">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -982,8 +1030,11 @@
       <c r="G18">
         <v>51.929931640625</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="V18">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1005,8 +1056,11 @@
       <c r="G19">
         <v>82.0498046875</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="V19">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1028,8 +1082,11 @@
       <c r="G20">
         <v>87.64990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="V20">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1048,8 +1105,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="V21">
+        <v>18.74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1071,8 +1131,11 @@
       <c r="G22">
         <v>53.25</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="V22">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1094,8 +1157,11 @@
       <c r="G23">
         <v>85.47998046875</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="V23">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1117,8 +1183,11 @@
       <c r="G24">
         <v>85.97998046875</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="V24">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1140,8 +1209,11 @@
       <c r="G25">
         <v>61.260009765625</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="V25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1157,8 +1229,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="V26">
+        <v>21.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1171,8 +1246,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="V27">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1194,8 +1272,11 @@
       <c r="G28">
         <v>53.14990234375</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="V28">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1217,8 +1298,11 @@
       <c r="G29">
         <v>109.75</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="V29">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1240,8 +1324,11 @@
       <c r="G30">
         <v>81.43017578125</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="V30">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1263,8 +1350,11 @@
       <c r="G31">
         <v>65.0498046875</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="V31">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1286,8 +1376,11 @@
       <c r="G32">
         <v>66.75</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="V32">
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1308,6 +1401,9 @@
       </c>
       <c r="G33">
         <v>81.64990234375</v>
+      </c>
+      <c r="V33">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 5</t>
+    <t>Parcial Rodada 6</t>
   </si>
   <si>
     <t>time_id</t>
@@ -624,10 +624,10 @@
         <v>58.679931640625</v>
       </c>
       <c r="G2">
-        <v>58.679931640625</v>
-      </c>
-      <c r="V2">
-        <v>15.5</v>
+        <v>94.6201171875</v>
+      </c>
+      <c r="H2">
+        <v>94.6201171875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -650,10 +650,10 @@
         <v>86.43017578125</v>
       </c>
       <c r="G3">
-        <v>86.43017578125</v>
-      </c>
-      <c r="V3">
-        <v>25.7</v>
+        <v>86.419921875</v>
+      </c>
+      <c r="H3">
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -676,10 +676,10 @@
         <v>50.590087890625</v>
       </c>
       <c r="G4">
-        <v>50.590087890625</v>
-      </c>
-      <c r="V4">
-        <v>20.7</v>
+        <v>81.169921875</v>
+      </c>
+      <c r="H4">
+        <v>81.169921875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -702,10 +702,10 @@
         <v>58.530029296875</v>
       </c>
       <c r="G5">
-        <v>58.530029296875</v>
-      </c>
-      <c r="V5">
-        <v>26.2</v>
+        <v>78.81982421875</v>
+      </c>
+      <c r="H5">
+        <v>78.81982421875</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -728,10 +728,10 @@
         <v>80.35986328125</v>
       </c>
       <c r="G6">
-        <v>80.35986328125</v>
-      </c>
-      <c r="V6">
-        <v>11.3</v>
+        <v>98.52001953125</v>
+      </c>
+      <c r="H6">
+        <v>98.52001953125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -754,10 +754,7 @@
         <v>77.259765625</v>
       </c>
       <c r="G7">
-        <v>77.259765625</v>
-      </c>
-      <c r="V7">
-        <v>20.17</v>
+        <v>69.3701171875</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -780,10 +777,10 @@
         <v>65.14990234375</v>
       </c>
       <c r="G8">
-        <v>65.14990234375</v>
-      </c>
-      <c r="V8">
-        <v>22.3</v>
+        <v>93.02001953125</v>
+      </c>
+      <c r="H8">
+        <v>93.02001953125</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -806,10 +803,10 @@
         <v>81.64990234375</v>
       </c>
       <c r="G9">
-        <v>81.64990234375</v>
-      </c>
-      <c r="V9">
-        <v>13.8</v>
+        <v>84.81982421875</v>
+      </c>
+      <c r="H9">
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -832,10 +829,10 @@
         <v>34.89990234375</v>
       </c>
       <c r="G10">
-        <v>34.89990234375</v>
-      </c>
-      <c r="V10">
-        <v>6</v>
+        <v>88.6201171875</v>
+      </c>
+      <c r="H10">
+        <v>88.6201171875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -858,10 +855,10 @@
         <v>73.22998046875</v>
       </c>
       <c r="G11">
-        <v>73.22998046875</v>
-      </c>
-      <c r="V11">
-        <v>16.59</v>
+        <v>79.33984375</v>
+      </c>
+      <c r="H11">
+        <v>79.33984375</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -884,10 +881,10 @@
         <v>65.14990234375</v>
       </c>
       <c r="G12">
-        <v>65.14990234375</v>
-      </c>
-      <c r="V12">
-        <v>22.3</v>
+        <v>93.02001953125</v>
+      </c>
+      <c r="H12">
+        <v>93.02001953125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -910,10 +907,10 @@
         <v>47.72998046875</v>
       </c>
       <c r="G13">
-        <v>47.72998046875</v>
-      </c>
-      <c r="V13">
-        <v>11.3</v>
+        <v>70.60009765625</v>
+      </c>
+      <c r="H13">
+        <v>70.60009765625</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -926,9 +923,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>18.7</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -950,10 +944,10 @@
         <v>74.9501953125</v>
       </c>
       <c r="G15">
-        <v>74.9501953125</v>
-      </c>
-      <c r="V15">
-        <v>41.6</v>
+        <v>103.919921875</v>
+      </c>
+      <c r="H15">
+        <v>103.919921875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -976,13 +970,13 @@
         <v>52.25</v>
       </c>
       <c r="G16">
-        <v>52.25</v>
-      </c>
-      <c r="V16">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>82.919921875</v>
+      </c>
+      <c r="H16">
+        <v>82.919921875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1002,13 +996,13 @@
         <v>45.64990234375</v>
       </c>
       <c r="G17">
-        <v>45.64990234375</v>
-      </c>
-      <c r="V17">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>72.27001953125</v>
+      </c>
+      <c r="H17">
+        <v>72.27001953125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1028,13 +1022,13 @@
         <v>51.929931640625</v>
       </c>
       <c r="G18">
-        <v>51.929931640625</v>
-      </c>
-      <c r="V18">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>74.77001953125</v>
+      </c>
+      <c r="H18">
+        <v>74.77001953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1054,13 +1048,13 @@
         <v>82.0498046875</v>
       </c>
       <c r="G19">
-        <v>82.0498046875</v>
-      </c>
-      <c r="V19">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>77.919921875</v>
+      </c>
+      <c r="H19">
+        <v>77.919921875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1080,13 +1074,13 @@
         <v>87.64990234375</v>
       </c>
       <c r="G20">
-        <v>87.64990234375</v>
-      </c>
-      <c r="V20">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>89.02001953125</v>
+      </c>
+      <c r="H20">
+        <v>89.02001953125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1105,11 +1099,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>18.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1129,13 +1120,13 @@
         <v>53.25</v>
       </c>
       <c r="G22">
-        <v>53.25</v>
-      </c>
-      <c r="V22">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>83.31982421875</v>
+      </c>
+      <c r="H22">
+        <v>83.31982421875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1155,13 +1146,13 @@
         <v>85.47998046875</v>
       </c>
       <c r="G23">
-        <v>85.47998046875</v>
-      </c>
-      <c r="V23">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>84.60986328125</v>
+      </c>
+      <c r="H23">
+        <v>84.60986328125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1181,13 +1172,13 @@
         <v>85.97998046875</v>
       </c>
       <c r="G24">
-        <v>85.97998046875</v>
-      </c>
-      <c r="V24">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>87.22021484375</v>
+      </c>
+      <c r="H24">
+        <v>87.22021484375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1207,13 +1198,13 @@
         <v>61.260009765625</v>
       </c>
       <c r="G25">
-        <v>61.260009765625</v>
-      </c>
-      <c r="V25">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>90.3701171875</v>
+      </c>
+      <c r="H25">
+        <v>90.3701171875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1229,11 +1220,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>21.85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1246,11 +1234,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>18.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1270,13 +1255,13 @@
         <v>53.14990234375</v>
       </c>
       <c r="G28">
-        <v>53.14990234375</v>
-      </c>
-      <c r="V28">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>87.52001953125</v>
+      </c>
+      <c r="H28">
+        <v>87.52001953125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1296,13 +1281,13 @@
         <v>109.75</v>
       </c>
       <c r="G29">
-        <v>109.75</v>
-      </c>
-      <c r="V29">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>81.47021484375</v>
+      </c>
+      <c r="H29">
+        <v>81.47021484375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1322,13 +1307,13 @@
         <v>81.43017578125</v>
       </c>
       <c r="G30">
-        <v>81.43017578125</v>
-      </c>
-      <c r="V30">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>85.669921875</v>
+      </c>
+      <c r="H30">
+        <v>85.669921875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1348,13 +1333,13 @@
         <v>65.0498046875</v>
       </c>
       <c r="G31">
-        <v>65.0498046875</v>
-      </c>
-      <c r="V31">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>95.6201171875</v>
+      </c>
+      <c r="H31">
+        <v>95.6201171875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1374,13 +1359,13 @@
         <v>66.75</v>
       </c>
       <c r="G32">
-        <v>66.75</v>
-      </c>
-      <c r="V32">
-        <v>69.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>107.56005859375</v>
+      </c>
+      <c r="H32">
+        <v>107.56005859375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1400,10 +1385,10 @@
         <v>81.64990234375</v>
       </c>
       <c r="G33">
-        <v>81.64990234375</v>
-      </c>
-      <c r="V33">
-        <v>9.300000000000001</v>
+        <v>74.31982421875</v>
+      </c>
+      <c r="H33">
+        <v>74.31982421875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -109,7 +109,7 @@
     <t>PUXE FC</t>
   </si>
   <si>
-    <t>NaoVaiDescer!</t>
+    <t>VaiDescerkkkk!!!</t>
   </si>
   <si>
     <t>cartola scheuer17</t>
@@ -629,6 +629,9 @@
       <c r="H2">
         <v>94.6201171875</v>
       </c>
+      <c r="V2">
+        <v>68.8</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -655,6 +658,9 @@
       <c r="H3">
         <v>86.419921875</v>
       </c>
+      <c r="V3">
+        <v>47.39</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -681,6 +687,9 @@
       <c r="H4">
         <v>81.169921875</v>
       </c>
+      <c r="V4">
+        <v>62.92</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -707,6 +716,9 @@
       <c r="H5">
         <v>78.81982421875</v>
       </c>
+      <c r="V5">
+        <v>74.91</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -733,6 +745,9 @@
       <c r="H6">
         <v>98.52001953125</v>
       </c>
+      <c r="V6">
+        <v>77.41</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -756,6 +771,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -782,6 +800,9 @@
       <c r="H8">
         <v>93.02001953125</v>
       </c>
+      <c r="V8">
+        <v>83</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -808,6 +829,9 @@
       <c r="H9">
         <v>84.81982421875</v>
       </c>
+      <c r="V9">
+        <v>62.01</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -834,6 +858,9 @@
       <c r="H10">
         <v>88.6201171875</v>
       </c>
+      <c r="V10">
+        <v>58.89</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -860,6 +887,9 @@
       <c r="H11">
         <v>79.33984375</v>
       </c>
+      <c r="V11">
+        <v>68.69</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -886,6 +916,9 @@
       <c r="H12">
         <v>93.02001953125</v>
       </c>
+      <c r="V12">
+        <v>83</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -912,6 +945,9 @@
       <c r="H13">
         <v>70.60009765625</v>
       </c>
+      <c r="V13">
+        <v>44.51</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -923,6 +959,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>65.70999999999999</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -949,6 +988,9 @@
       <c r="H15">
         <v>103.919921875</v>
       </c>
+      <c r="V15">
+        <v>86.42</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -975,8 +1017,11 @@
       <c r="H16">
         <v>82.919921875</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="V16">
+        <v>54.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1001,8 +1046,11 @@
       <c r="H17">
         <v>72.27001953125</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="V17">
+        <v>53.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1027,8 +1075,11 @@
       <c r="H18">
         <v>74.77001953125</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="V18">
+        <v>66.51000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1053,8 +1104,11 @@
       <c r="H19">
         <v>77.919921875</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="V19">
+        <v>73.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1079,8 +1133,11 @@
       <c r="H20">
         <v>89.02001953125</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="V20">
+        <v>62.81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1099,8 +1156,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="V21">
+        <v>71.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1125,8 +1185,11 @@
       <c r="H22">
         <v>83.31982421875</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="V22">
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1151,8 +1214,11 @@
       <c r="H23">
         <v>84.60986328125</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="V23">
+        <v>72.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1177,8 +1243,11 @@
       <c r="H24">
         <v>87.22021484375</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="V24">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1203,8 +1272,11 @@
       <c r="H25">
         <v>90.3701171875</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="V25">
+        <v>72.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1220,8 +1292,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="V26">
+        <v>58.69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1234,8 +1309,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="V27">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1260,8 +1338,11 @@
       <c r="H28">
         <v>87.52001953125</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="V28">
+        <v>69.12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1286,8 +1367,11 @@
       <c r="H29">
         <v>81.47021484375</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="V29">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1312,8 +1396,11 @@
       <c r="H30">
         <v>85.669921875</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="V30">
+        <v>58.61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1338,8 +1425,11 @@
       <c r="H31">
         <v>95.6201171875</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="V31">
+        <v>69.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1364,8 +1454,11 @@
       <c r="H32">
         <v>107.56005859375</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="V32">
+        <v>71.61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1389,6 +1482,9 @@
       </c>
       <c r="H33">
         <v>74.31982421875</v>
+      </c>
+      <c r="V33">
+        <v>64.36</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 6</t>
+    <t>Parcial Rodada 7</t>
   </si>
   <si>
     <t>time_id</t>
@@ -627,10 +627,10 @@
         <v>94.6201171875</v>
       </c>
       <c r="H2">
-        <v>94.6201171875</v>
-      </c>
-      <c r="V2">
-        <v>68.8</v>
+        <v>68.7998046875</v>
+      </c>
+      <c r="I2">
+        <v>68.7998046875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -656,10 +656,10 @@
         <v>86.419921875</v>
       </c>
       <c r="H3">
-        <v>86.419921875</v>
-      </c>
-      <c r="V3">
-        <v>47.39</v>
+        <v>47.389892578125</v>
+      </c>
+      <c r="I3">
+        <v>47.389892578125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -685,10 +685,10 @@
         <v>81.169921875</v>
       </c>
       <c r="H4">
-        <v>81.169921875</v>
-      </c>
-      <c r="V4">
-        <v>62.92</v>
+        <v>62.919921875</v>
+      </c>
+      <c r="I4">
+        <v>62.919921875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -714,10 +714,10 @@
         <v>78.81982421875</v>
       </c>
       <c r="H5">
-        <v>78.81982421875</v>
-      </c>
-      <c r="V5">
-        <v>74.91</v>
+        <v>74.91015625</v>
+      </c>
+      <c r="I5">
+        <v>74.91015625</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -743,10 +743,10 @@
         <v>98.52001953125</v>
       </c>
       <c r="H6">
-        <v>98.52001953125</v>
-      </c>
-      <c r="V6">
-        <v>77.41</v>
+        <v>77.41015625</v>
+      </c>
+      <c r="I6">
+        <v>77.41015625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -771,9 +771,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>52.2</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -798,9 +795,9 @@
         <v>93.02001953125</v>
       </c>
       <c r="H8">
-        <v>93.02001953125</v>
-      </c>
-      <c r="V8">
+        <v>83</v>
+      </c>
+      <c r="I8">
         <v>83</v>
       </c>
     </row>
@@ -827,10 +824,10 @@
         <v>84.81982421875</v>
       </c>
       <c r="H9">
-        <v>84.81982421875</v>
-      </c>
-      <c r="V9">
-        <v>62.01</v>
+        <v>62.010009765625</v>
+      </c>
+      <c r="I9">
+        <v>62.010009765625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -856,10 +853,10 @@
         <v>88.6201171875</v>
       </c>
       <c r="H10">
-        <v>88.6201171875</v>
-      </c>
-      <c r="V10">
-        <v>58.89</v>
+        <v>58.889892578125</v>
+      </c>
+      <c r="I10">
+        <v>58.889892578125</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -885,10 +882,10 @@
         <v>79.33984375</v>
       </c>
       <c r="H11">
-        <v>79.33984375</v>
-      </c>
-      <c r="V11">
-        <v>68.69</v>
+        <v>68.68994140625</v>
+      </c>
+      <c r="I11">
+        <v>68.68994140625</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -914,9 +911,9 @@
         <v>93.02001953125</v>
       </c>
       <c r="H12">
-        <v>93.02001953125</v>
-      </c>
-      <c r="V12">
+        <v>83</v>
+      </c>
+      <c r="I12">
         <v>83</v>
       </c>
     </row>
@@ -943,10 +940,7 @@
         <v>70.60009765625</v>
       </c>
       <c r="H13">
-        <v>70.60009765625</v>
-      </c>
-      <c r="V13">
-        <v>44.51</v>
+        <v>44.510009765625</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -959,9 +953,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>65.70999999999999</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -986,10 +977,10 @@
         <v>103.919921875</v>
       </c>
       <c r="H15">
-        <v>103.919921875</v>
-      </c>
-      <c r="V15">
-        <v>86.42</v>
+        <v>86.419921875</v>
+      </c>
+      <c r="I15">
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1015,13 +1006,13 @@
         <v>82.919921875</v>
       </c>
       <c r="H16">
-        <v>82.919921875</v>
-      </c>
-      <c r="V16">
-        <v>54.21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>54.2099609375</v>
+      </c>
+      <c r="I16">
+        <v>54.2099609375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1044,13 +1035,13 @@
         <v>72.27001953125</v>
       </c>
       <c r="H17">
-        <v>72.27001953125</v>
-      </c>
-      <c r="V17">
-        <v>53.46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>53.4599609375</v>
+      </c>
+      <c r="I17">
+        <v>53.4599609375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1073,13 +1064,13 @@
         <v>74.77001953125</v>
       </c>
       <c r="H18">
-        <v>74.77001953125</v>
-      </c>
-      <c r="V18">
-        <v>66.51000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>66.509765625</v>
+      </c>
+      <c r="I18">
+        <v>66.509765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1102,13 +1093,13 @@
         <v>77.919921875</v>
       </c>
       <c r="H19">
-        <v>77.919921875</v>
-      </c>
-      <c r="V19">
-        <v>73.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>73.22021484375</v>
+      </c>
+      <c r="I19">
+        <v>73.22021484375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1131,13 +1122,13 @@
         <v>89.02001953125</v>
       </c>
       <c r="H20">
-        <v>89.02001953125</v>
-      </c>
-      <c r="V20">
-        <v>62.81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>62.81005859375</v>
+      </c>
+      <c r="I20">
+        <v>62.81005859375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1156,11 +1147,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>71.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1183,13 +1171,13 @@
         <v>83.31982421875</v>
       </c>
       <c r="H22">
-        <v>83.31982421875</v>
-      </c>
-      <c r="V22">
-        <v>54.81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>54.81005859375</v>
+      </c>
+      <c r="I22">
+        <v>54.81005859375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1212,13 +1200,13 @@
         <v>84.60986328125</v>
       </c>
       <c r="H23">
-        <v>84.60986328125</v>
-      </c>
-      <c r="V23">
-        <v>72.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>72.10986328125</v>
+      </c>
+      <c r="I23">
+        <v>72.10986328125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1241,13 +1229,13 @@
         <v>87.22021484375</v>
       </c>
       <c r="H24">
-        <v>87.22021484375</v>
-      </c>
-      <c r="V24">
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>62.10009765625</v>
+      </c>
+      <c r="I24">
+        <v>62.10009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1270,13 +1258,13 @@
         <v>90.3701171875</v>
       </c>
       <c r="H25">
-        <v>90.3701171875</v>
-      </c>
-      <c r="V25">
-        <v>72.09</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>72.08984375</v>
+      </c>
+      <c r="I25">
+        <v>72.08984375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1292,11 +1280,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>58.69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1309,11 +1294,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1336,13 +1318,13 @@
         <v>87.52001953125</v>
       </c>
       <c r="H28">
-        <v>87.52001953125</v>
-      </c>
-      <c r="V28">
-        <v>69.12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>69.1201171875</v>
+      </c>
+      <c r="I28">
+        <v>69.1201171875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1365,13 +1347,13 @@
         <v>81.47021484375</v>
       </c>
       <c r="H29">
-        <v>81.47021484375</v>
-      </c>
-      <c r="V29">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>56.39990234375</v>
+      </c>
+      <c r="I29">
+        <v>56.39990234375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1394,13 +1376,13 @@
         <v>85.669921875</v>
       </c>
       <c r="H30">
-        <v>85.669921875</v>
-      </c>
-      <c r="V30">
-        <v>58.61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>58.610107421875</v>
+      </c>
+      <c r="I30">
+        <v>58.610107421875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1423,13 +1405,13 @@
         <v>95.6201171875</v>
       </c>
       <c r="H31">
-        <v>95.6201171875</v>
-      </c>
-      <c r="V31">
-        <v>69.42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>69.419921875</v>
+      </c>
+      <c r="I31">
+        <v>69.419921875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1452,13 +1434,13 @@
         <v>107.56005859375</v>
       </c>
       <c r="H32">
-        <v>107.56005859375</v>
-      </c>
-      <c r="V32">
-        <v>71.61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>71.60986328125</v>
+      </c>
+      <c r="I32">
+        <v>71.60986328125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1481,10 +1463,10 @@
         <v>74.31982421875</v>
       </c>
       <c r="H33">
-        <v>74.31982421875</v>
-      </c>
-      <c r="V33">
-        <v>64.36</v>
+        <v>64.35986328125</v>
+      </c>
+      <c r="I33">
+        <v>64.35986328125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -632,6 +632,9 @@
       <c r="I2">
         <v>68.7998046875</v>
       </c>
+      <c r="V2">
+        <v>35.87</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -661,6 +664,9 @@
       <c r="I3">
         <v>47.389892578125</v>
       </c>
+      <c r="V3">
+        <v>38.87</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -690,6 +696,9 @@
       <c r="I4">
         <v>62.919921875</v>
       </c>
+      <c r="V4">
+        <v>35.8</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -719,6 +728,9 @@
       <c r="I5">
         <v>74.91015625</v>
       </c>
+      <c r="V5">
+        <v>29.97</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -748,6 +760,9 @@
       <c r="I6">
         <v>77.41015625</v>
       </c>
+      <c r="V6">
+        <v>37.57</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -771,6 +786,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>22.97</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -800,6 +818,9 @@
       <c r="I8">
         <v>83</v>
       </c>
+      <c r="V8">
+        <v>43.17</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -829,6 +850,9 @@
       <c r="I9">
         <v>62.010009765625</v>
       </c>
+      <c r="V9">
+        <v>30.77</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -858,6 +882,9 @@
       <c r="I10">
         <v>58.889892578125</v>
       </c>
+      <c r="V10">
+        <v>36.17</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -887,6 +914,9 @@
       <c r="I11">
         <v>68.68994140625</v>
       </c>
+      <c r="V11">
+        <v>33.6</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -916,6 +946,9 @@
       <c r="I12">
         <v>83</v>
       </c>
+      <c r="V12">
+        <v>43.17</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -942,6 +975,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -953,6 +989,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>50.87</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -982,6 +1021,9 @@
       <c r="I15">
         <v>86.419921875</v>
       </c>
+      <c r="V15">
+        <v>45.77</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1011,8 +1053,11 @@
       <c r="I16">
         <v>54.2099609375</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="V16">
+        <v>28.47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1040,8 +1085,11 @@
       <c r="I17">
         <v>53.4599609375</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="V17">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1069,8 +1117,11 @@
       <c r="I18">
         <v>66.509765625</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="V18">
+        <v>70.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1098,8 +1149,11 @@
       <c r="I19">
         <v>73.22021484375</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="V19">
+        <v>48.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1127,8 +1181,11 @@
       <c r="I20">
         <v>62.81005859375</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="V20">
+        <v>69.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1147,8 +1204,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="V21">
+        <v>28.77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1176,8 +1236,11 @@
       <c r="I22">
         <v>54.81005859375</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="V22">
+        <v>23.67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1205,8 +1268,11 @@
       <c r="I23">
         <v>72.10986328125</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="V23">
+        <v>45.87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1234,8 +1300,11 @@
       <c r="I24">
         <v>62.10009765625</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="V24">
+        <v>66.01000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1263,8 +1332,11 @@
       <c r="I25">
         <v>72.08984375</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="V25">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1280,8 +1352,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="V26">
+        <v>27.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1294,8 +1369,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="V27">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1323,8 +1401,11 @@
       <c r="I28">
         <v>69.1201171875</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="V28">
+        <v>39.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1352,8 +1433,11 @@
       <c r="I29">
         <v>56.39990234375</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="V29">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1381,8 +1465,11 @@
       <c r="I30">
         <v>58.610107421875</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="V30">
+        <v>45.37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1410,8 +1497,11 @@
       <c r="I31">
         <v>69.419921875</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="V31">
+        <v>40.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1439,8 +1529,11 @@
       <c r="I32">
         <v>71.60986328125</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="V32">
+        <v>33.27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1467,6 +1560,9 @@
       </c>
       <c r="I33">
         <v>64.35986328125</v>
+      </c>
+      <c r="V33">
+        <v>30.67</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 7</t>
+    <t>Parcial Rodada 8</t>
   </si>
   <si>
     <t>time_id</t>
@@ -630,10 +630,10 @@
         <v>68.7998046875</v>
       </c>
       <c r="I2">
-        <v>68.7998046875</v>
-      </c>
-      <c r="V2">
-        <v>35.87</v>
+        <v>50.570068359375</v>
+      </c>
+      <c r="J2">
+        <v>50.570068359375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -662,10 +662,10 @@
         <v>47.389892578125</v>
       </c>
       <c r="I3">
-        <v>47.389892578125</v>
-      </c>
-      <c r="V3">
-        <v>38.87</v>
+        <v>67.27001953125</v>
+      </c>
+      <c r="J3">
+        <v>67.27001953125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -694,10 +694,10 @@
         <v>62.919921875</v>
       </c>
       <c r="I4">
-        <v>62.919921875</v>
-      </c>
-      <c r="V4">
-        <v>35.8</v>
+        <v>87.009765625</v>
+      </c>
+      <c r="J4">
+        <v>87.009765625</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -726,10 +726,10 @@
         <v>74.91015625</v>
       </c>
       <c r="I5">
-        <v>74.91015625</v>
-      </c>
-      <c r="V5">
-        <v>29.97</v>
+        <v>60.27001953125</v>
+      </c>
+      <c r="J5">
+        <v>60.27001953125</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -758,10 +758,10 @@
         <v>77.41015625</v>
       </c>
       <c r="I6">
-        <v>77.41015625</v>
-      </c>
-      <c r="V6">
-        <v>37.57</v>
+        <v>71.3701171875</v>
+      </c>
+      <c r="J6">
+        <v>71.3701171875</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -786,9 +786,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>22.97</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -816,10 +813,10 @@
         <v>83</v>
       </c>
       <c r="I8">
-        <v>83</v>
-      </c>
-      <c r="V8">
-        <v>43.17</v>
+        <v>76.97021484375</v>
+      </c>
+      <c r="J8">
+        <v>76.97021484375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -848,10 +845,10 @@
         <v>62.010009765625</v>
       </c>
       <c r="I9">
-        <v>62.010009765625</v>
-      </c>
-      <c r="V9">
-        <v>30.77</v>
+        <v>77.06982421875</v>
+      </c>
+      <c r="J9">
+        <v>77.06982421875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -880,10 +877,10 @@
         <v>58.889892578125</v>
       </c>
       <c r="I10">
-        <v>58.889892578125</v>
-      </c>
-      <c r="V10">
-        <v>36.17</v>
+        <v>60.070068359375</v>
+      </c>
+      <c r="J10">
+        <v>60.070068359375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -912,10 +909,10 @@
         <v>68.68994140625</v>
       </c>
       <c r="I11">
-        <v>68.68994140625</v>
-      </c>
-      <c r="V11">
-        <v>33.6</v>
+        <v>61.570068359375</v>
+      </c>
+      <c r="J11">
+        <v>61.570068359375</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -944,10 +941,10 @@
         <v>83</v>
       </c>
       <c r="I12">
-        <v>83</v>
-      </c>
-      <c r="V12">
-        <v>43.17</v>
+        <v>85.97021484375</v>
+      </c>
+      <c r="J12">
+        <v>85.97021484375</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -975,9 +972,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>47</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -989,9 +983,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>50.87</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1019,10 +1010,10 @@
         <v>86.419921875</v>
       </c>
       <c r="I15">
-        <v>86.419921875</v>
-      </c>
-      <c r="V15">
-        <v>45.77</v>
+        <v>82.3701171875</v>
+      </c>
+      <c r="J15">
+        <v>82.3701171875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1051,13 +1042,10 @@
         <v>54.2099609375</v>
       </c>
       <c r="I16">
-        <v>54.2099609375</v>
-      </c>
-      <c r="V16">
-        <v>28.47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>49.469970703125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1083,13 +1071,13 @@
         <v>53.4599609375</v>
       </c>
       <c r="I17">
-        <v>53.4599609375</v>
-      </c>
-      <c r="V17">
-        <v>32.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>58.669921875</v>
+      </c>
+      <c r="J17">
+        <v>58.669921875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1115,13 +1103,13 @@
         <v>66.509765625</v>
       </c>
       <c r="I18">
-        <v>66.509765625</v>
-      </c>
-      <c r="V18">
-        <v>70.17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>82.56982421875</v>
+      </c>
+      <c r="J18">
+        <v>82.56982421875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1147,13 +1135,13 @@
         <v>73.22021484375</v>
       </c>
       <c r="I19">
-        <v>73.22021484375</v>
-      </c>
-      <c r="V19">
-        <v>48.87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>75.56982421875</v>
+      </c>
+      <c r="J19">
+        <v>75.56982421875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1179,13 +1167,13 @@
         <v>62.81005859375</v>
       </c>
       <c r="I20">
-        <v>62.81005859375</v>
-      </c>
-      <c r="V20">
-        <v>69.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>105.8701171875</v>
+      </c>
+      <c r="J20">
+        <v>105.8701171875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1204,11 +1192,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>28.77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1234,13 +1219,13 @@
         <v>54.81005859375</v>
       </c>
       <c r="I22">
-        <v>54.81005859375</v>
-      </c>
-      <c r="V22">
-        <v>23.67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>79.919921875</v>
+      </c>
+      <c r="J22">
+        <v>79.919921875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1266,13 +1251,13 @@
         <v>72.10986328125</v>
       </c>
       <c r="I23">
-        <v>72.10986328125</v>
-      </c>
-      <c r="V23">
-        <v>45.87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>87.1201171875</v>
+      </c>
+      <c r="J23">
+        <v>87.1201171875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1298,13 +1283,13 @@
         <v>62.10009765625</v>
       </c>
       <c r="I24">
-        <v>62.10009765625</v>
-      </c>
-      <c r="V24">
-        <v>66.01000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>82.81005859375</v>
+      </c>
+      <c r="J24">
+        <v>82.81005859375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1330,13 +1315,13 @@
         <v>72.08984375</v>
       </c>
       <c r="I25">
-        <v>72.08984375</v>
-      </c>
-      <c r="V25">
-        <v>60.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>89.06005859375</v>
+      </c>
+      <c r="J25">
+        <v>89.06005859375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1352,11 +1337,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>27.32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1369,11 +1351,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1399,13 +1378,13 @@
         <v>69.1201171875</v>
       </c>
       <c r="I28">
-        <v>69.1201171875</v>
-      </c>
-      <c r="V28">
-        <v>39.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>79.47021484375</v>
+      </c>
+      <c r="J28">
+        <v>79.47021484375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1431,13 +1410,13 @@
         <v>56.39990234375</v>
       </c>
       <c r="I29">
-        <v>56.39990234375</v>
-      </c>
-      <c r="V29">
-        <v>36.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>59.56005859375</v>
+      </c>
+      <c r="J29">
+        <v>59.56005859375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1463,13 +1442,13 @@
         <v>58.610107421875</v>
       </c>
       <c r="I30">
-        <v>58.610107421875</v>
-      </c>
-      <c r="V30">
-        <v>45.37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>81.56982421875</v>
+      </c>
+      <c r="J30">
+        <v>81.56982421875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1495,13 +1474,13 @@
         <v>69.419921875</v>
       </c>
       <c r="I31">
-        <v>69.419921875</v>
-      </c>
-      <c r="V31">
-        <v>40.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>70.47021484375</v>
+      </c>
+      <c r="J31">
+        <v>70.47021484375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1527,13 +1506,13 @@
         <v>71.60986328125</v>
       </c>
       <c r="I32">
-        <v>71.60986328125</v>
-      </c>
-      <c r="V32">
-        <v>33.27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>94.8701171875</v>
+      </c>
+      <c r="J32">
+        <v>94.8701171875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1559,10 +1538,10 @@
         <v>64.35986328125</v>
       </c>
       <c r="I33">
-        <v>64.35986328125</v>
-      </c>
-      <c r="V33">
-        <v>30.67</v>
+        <v>76.97021484375</v>
+      </c>
+      <c r="J33">
+        <v>76.97021484375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 8</t>
+    <t>Parcial Rodada 9</t>
   </si>
   <si>
     <t>time_id</t>
@@ -633,7 +633,10 @@
         <v>50.570068359375</v>
       </c>
       <c r="J2">
-        <v>50.570068359375</v>
+        <v>79.14990234375</v>
+      </c>
+      <c r="K2">
+        <v>79.14990234375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -665,7 +668,10 @@
         <v>67.27001953125</v>
       </c>
       <c r="J3">
-        <v>67.27001953125</v>
+        <v>75.75</v>
+      </c>
+      <c r="K3">
+        <v>75.75</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -697,7 +703,10 @@
         <v>87.009765625</v>
       </c>
       <c r="J4">
-        <v>87.009765625</v>
+        <v>69.89990234375</v>
+      </c>
+      <c r="K4">
+        <v>69.89990234375</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -729,7 +738,10 @@
         <v>60.27001953125</v>
       </c>
       <c r="J5">
-        <v>60.27001953125</v>
+        <v>75</v>
+      </c>
+      <c r="K5">
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -761,7 +773,10 @@
         <v>71.3701171875</v>
       </c>
       <c r="J6">
-        <v>71.3701171875</v>
+        <v>80.75</v>
+      </c>
+      <c r="K6">
+        <v>80.75</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -816,7 +831,10 @@
         <v>76.97021484375</v>
       </c>
       <c r="J8">
-        <v>76.97021484375</v>
+        <v>76.4501953125</v>
+      </c>
+      <c r="K8">
+        <v>76.4501953125</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -848,7 +866,10 @@
         <v>77.06982421875</v>
       </c>
       <c r="J9">
-        <v>77.06982421875</v>
+        <v>80.0498046875</v>
+      </c>
+      <c r="K9">
+        <v>80.0498046875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -880,7 +901,10 @@
         <v>60.070068359375</v>
       </c>
       <c r="J10">
-        <v>60.070068359375</v>
+        <v>79.85009765625</v>
+      </c>
+      <c r="K10">
+        <v>79.85009765625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -912,7 +936,10 @@
         <v>61.570068359375</v>
       </c>
       <c r="J11">
-        <v>61.570068359375</v>
+        <v>74.2998046875</v>
+      </c>
+      <c r="K11">
+        <v>74.2998046875</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -944,7 +971,10 @@
         <v>85.97021484375</v>
       </c>
       <c r="J12">
-        <v>85.97021484375</v>
+        <v>76.4501953125</v>
+      </c>
+      <c r="K12">
+        <v>76.4501953125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1013,7 +1043,10 @@
         <v>82.3701171875</v>
       </c>
       <c r="J15">
-        <v>82.3701171875</v>
+        <v>79.60009765625</v>
+      </c>
+      <c r="K15">
+        <v>79.60009765625</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1045,7 +1078,7 @@
         <v>49.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1074,10 +1107,10 @@
         <v>58.669921875</v>
       </c>
       <c r="J17">
-        <v>58.669921875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>45.699951171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1106,10 +1139,13 @@
         <v>82.56982421875</v>
       </c>
       <c r="J18">
-        <v>82.56982421875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>76.25</v>
+      </c>
+      <c r="K18">
+        <v>76.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1138,10 +1174,13 @@
         <v>75.56982421875</v>
       </c>
       <c r="J19">
-        <v>75.56982421875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>72.2998046875</v>
+      </c>
+      <c r="K19">
+        <v>72.2998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1170,10 +1209,13 @@
         <v>105.8701171875</v>
       </c>
       <c r="J20">
-        <v>105.8701171875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>76.89990234375</v>
+      </c>
+      <c r="K20">
+        <v>76.89990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1193,7 +1235,7 @@
         <v>27.4300537109375</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1222,10 +1264,13 @@
         <v>79.919921875</v>
       </c>
       <c r="J22">
-        <v>79.919921875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>72.25</v>
+      </c>
+      <c r="K22">
+        <v>72.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1254,10 +1299,13 @@
         <v>87.1201171875</v>
       </c>
       <c r="J23">
-        <v>87.1201171875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>55.0400390625</v>
+      </c>
+      <c r="K23">
+        <v>55.0400390625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1286,10 +1334,13 @@
         <v>82.81005859375</v>
       </c>
       <c r="J24">
-        <v>82.81005859375</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>91.39990234375</v>
+      </c>
+      <c r="K24">
+        <v>91.39990234375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1318,10 +1369,13 @@
         <v>89.06005859375</v>
       </c>
       <c r="J25">
-        <v>89.06005859375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>61.570068359375</v>
+      </c>
+      <c r="K25">
+        <v>61.570068359375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1338,7 +1392,7 @@
         <v>65.259765625</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1352,7 +1406,7 @@
         <v>36.429931640625</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:11">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1381,10 +1435,13 @@
         <v>79.47021484375</v>
       </c>
       <c r="J28">
-        <v>79.47021484375</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>80.5498046875</v>
+      </c>
+      <c r="K28">
+        <v>80.5498046875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1413,10 +1470,13 @@
         <v>59.56005859375</v>
       </c>
       <c r="J29">
-        <v>59.56005859375</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>75.0498046875</v>
+      </c>
+      <c r="K29">
+        <v>75.0498046875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1445,10 +1505,13 @@
         <v>81.56982421875</v>
       </c>
       <c r="J30">
-        <v>81.56982421875</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>73.35009765625</v>
+      </c>
+      <c r="K30">
+        <v>73.35009765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1477,10 +1540,13 @@
         <v>70.47021484375</v>
       </c>
       <c r="J31">
-        <v>70.47021484375</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>74.9501953125</v>
+      </c>
+      <c r="K31">
+        <v>74.9501953125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1509,10 +1575,13 @@
         <v>94.8701171875</v>
       </c>
       <c r="J32">
-        <v>94.8701171875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>74.0498046875</v>
+      </c>
+      <c r="K32">
+        <v>74.0498046875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1541,7 +1610,10 @@
         <v>76.97021484375</v>
       </c>
       <c r="J33">
-        <v>76.97021484375</v>
+        <v>84.85009765625</v>
+      </c>
+      <c r="K33">
+        <v>84.85009765625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -638,6 +638,9 @@
       <c r="K2">
         <v>79.14990234375</v>
       </c>
+      <c r="V2">
+        <v>71.88</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -673,6 +676,9 @@
       <c r="K3">
         <v>75.75</v>
       </c>
+      <c r="V3">
+        <v>85.95999999999999</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -708,6 +714,9 @@
       <c r="K4">
         <v>69.89990234375</v>
       </c>
+      <c r="V4">
+        <v>92.14</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -743,6 +752,9 @@
       <c r="K5">
         <v>75</v>
       </c>
+      <c r="V5">
+        <v>86.04000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -778,6 +790,9 @@
       <c r="K6">
         <v>80.75</v>
       </c>
+      <c r="V6">
+        <v>84.73999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -801,6 +816,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>65.7</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -836,6 +854,9 @@
       <c r="K8">
         <v>76.4501953125</v>
       </c>
+      <c r="V8">
+        <v>86.25</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -871,6 +892,9 @@
       <c r="K9">
         <v>80.0498046875</v>
       </c>
+      <c r="V9">
+        <v>61.01</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -906,6 +930,9 @@
       <c r="K10">
         <v>79.85009765625</v>
       </c>
+      <c r="V10">
+        <v>101.96</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -941,6 +968,9 @@
       <c r="K11">
         <v>74.2998046875</v>
       </c>
+      <c r="V11">
+        <v>77.45</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -976,6 +1006,9 @@
       <c r="K12">
         <v>76.4501953125</v>
       </c>
+      <c r="V12">
+        <v>86.25</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1002,6 +1035,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>84.95</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1013,6 +1049,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>91.44</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1048,6 +1087,9 @@
       <c r="K15">
         <v>79.60009765625</v>
       </c>
+      <c r="V15">
+        <v>72.75</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1077,8 +1119,11 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="V16">
+        <v>81.73999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1109,8 +1154,11 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="V17">
+        <v>68.84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1144,8 +1192,11 @@
       <c r="K18">
         <v>76.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="V18">
+        <v>57.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1179,8 +1230,11 @@
       <c r="K19">
         <v>72.2998046875</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="V19">
+        <v>112.88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1214,8 +1268,11 @@
       <c r="K20">
         <v>76.89990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="V20">
+        <v>81.73999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1234,8 +1291,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="V21">
+        <v>45.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1269,8 +1329,11 @@
       <c r="K22">
         <v>72.25</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="V22">
+        <v>59.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1304,8 +1367,11 @@
       <c r="K23">
         <v>55.0400390625</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="V23">
+        <v>94.18000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1339,8 +1405,11 @@
       <c r="K24">
         <v>91.39990234375</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="V24">
+        <v>108.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1374,8 +1443,11 @@
       <c r="K25">
         <v>61.570068359375</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="V25">
+        <v>88.08</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1391,8 +1463,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="V26">
+        <v>72.84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1405,8 +1480,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="V27">
+        <v>72.84999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1440,8 +1518,11 @@
       <c r="K28">
         <v>80.5498046875</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="V28">
+        <v>65.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1475,8 +1556,11 @@
       <c r="K29">
         <v>75.0498046875</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="V29">
+        <v>98.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1510,8 +1594,11 @@
       <c r="K30">
         <v>73.35009765625</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="V30">
+        <v>104.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1545,8 +1632,11 @@
       <c r="K31">
         <v>74.9501953125</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="V31">
+        <v>90.68000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1580,8 +1670,11 @@
       <c r="K32">
         <v>74.0498046875</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="V32">
+        <v>91.18000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1614,6 +1707,9 @@
       </c>
       <c r="K33">
         <v>84.85009765625</v>
+      </c>
+      <c r="V33">
+        <v>86.36</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 9</t>
+    <t>Parcial Rodada 10</t>
   </si>
   <si>
     <t>time_id</t>
@@ -636,10 +636,10 @@
         <v>79.14990234375</v>
       </c>
       <c r="K2">
-        <v>79.14990234375</v>
-      </c>
-      <c r="V2">
-        <v>71.88</v>
+        <v>72.080078125</v>
+      </c>
+      <c r="L2">
+        <v>72.080078125</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -674,10 +674,10 @@
         <v>75.75</v>
       </c>
       <c r="K3">
-        <v>75.75</v>
-      </c>
-      <c r="V3">
-        <v>85.95999999999999</v>
+        <v>85.9599609375</v>
+      </c>
+      <c r="L3">
+        <v>85.9599609375</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -712,10 +712,10 @@
         <v>69.89990234375</v>
       </c>
       <c r="K4">
-        <v>69.89990234375</v>
-      </c>
-      <c r="V4">
-        <v>92.14</v>
+        <v>91.14013671875</v>
+      </c>
+      <c r="L4">
+        <v>91.14013671875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -750,10 +750,10 @@
         <v>75</v>
       </c>
       <c r="K5">
-        <v>75</v>
-      </c>
-      <c r="V5">
-        <v>86.04000000000001</v>
+        <v>86.0400390625</v>
+      </c>
+      <c r="L5">
+        <v>86.0400390625</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -788,10 +788,10 @@
         <v>80.75</v>
       </c>
       <c r="K6">
-        <v>80.75</v>
-      </c>
-      <c r="V6">
-        <v>84.73999999999999</v>
+        <v>84.43994140625</v>
+      </c>
+      <c r="L6">
+        <v>84.43994140625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -816,9 +816,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>65.7</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -852,10 +849,10 @@
         <v>76.4501953125</v>
       </c>
       <c r="K8">
-        <v>76.4501953125</v>
-      </c>
-      <c r="V8">
-        <v>86.25</v>
+        <v>85.85009765625</v>
+      </c>
+      <c r="L8">
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -890,10 +887,10 @@
         <v>80.0498046875</v>
       </c>
       <c r="K9">
-        <v>80.0498046875</v>
-      </c>
-      <c r="V9">
-        <v>61.01</v>
+        <v>59.010009765625</v>
+      </c>
+      <c r="L9">
+        <v>59.010009765625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -928,10 +925,10 @@
         <v>79.85009765625</v>
       </c>
       <c r="K10">
-        <v>79.85009765625</v>
-      </c>
-      <c r="V10">
-        <v>101.96</v>
+        <v>101.9599609375</v>
+      </c>
+      <c r="L10">
+        <v>101.9599609375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -966,10 +963,10 @@
         <v>74.2998046875</v>
       </c>
       <c r="K11">
-        <v>74.2998046875</v>
-      </c>
-      <c r="V11">
-        <v>77.45</v>
+        <v>77.4501953125</v>
+      </c>
+      <c r="L11">
+        <v>77.4501953125</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1004,10 +1001,10 @@
         <v>76.4501953125</v>
       </c>
       <c r="K12">
-        <v>76.4501953125</v>
-      </c>
-      <c r="V12">
-        <v>86.25</v>
+        <v>85.85009765625</v>
+      </c>
+      <c r="L12">
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1035,9 +1032,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>84.95</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1049,9 +1043,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>91.44</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1085,10 +1076,10 @@
         <v>79.60009765625</v>
       </c>
       <c r="K15">
-        <v>79.60009765625</v>
-      </c>
-      <c r="V15">
-        <v>72.75</v>
+        <v>71.0498046875</v>
+      </c>
+      <c r="L15">
+        <v>71.0498046875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1119,11 +1110,8 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-      <c r="V16">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1154,11 +1142,8 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-      <c r="V17">
-        <v>68.84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1190,13 +1175,10 @@
         <v>76.25</v>
       </c>
       <c r="K18">
-        <v>76.25</v>
-      </c>
-      <c r="V18">
-        <v>57.19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+        <v>56.090087890625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1228,13 +1210,13 @@
         <v>72.2998046875</v>
       </c>
       <c r="K19">
-        <v>72.2998046875</v>
-      </c>
-      <c r="V19">
-        <v>112.88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>112.8798828125</v>
+      </c>
+      <c r="L19">
+        <v>112.8798828125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1266,13 +1248,13 @@
         <v>76.89990234375</v>
       </c>
       <c r="K20">
-        <v>76.89990234375</v>
-      </c>
-      <c r="V20">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>79.93994140625</v>
+      </c>
+      <c r="L20">
+        <v>79.93994140625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1291,11 +1273,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>45.16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1327,13 +1306,13 @@
         <v>72.25</v>
       </c>
       <c r="K22">
-        <v>72.25</v>
-      </c>
-      <c r="V22">
-        <v>59.18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>59.3798828125</v>
+      </c>
+      <c r="L22">
+        <v>59.3798828125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1365,13 +1344,13 @@
         <v>55.0400390625</v>
       </c>
       <c r="K23">
-        <v>55.0400390625</v>
-      </c>
-      <c r="V23">
-        <v>94.18000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>93.8798828125</v>
+      </c>
+      <c r="L23">
+        <v>93.8798828125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1403,13 +1382,13 @@
         <v>91.39990234375</v>
       </c>
       <c r="K24">
-        <v>91.39990234375</v>
-      </c>
-      <c r="V24">
-        <v>108.94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>108.93994140625</v>
+      </c>
+      <c r="L24">
+        <v>108.93994140625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1441,13 +1420,13 @@
         <v>61.570068359375</v>
       </c>
       <c r="K25">
-        <v>61.570068359375</v>
-      </c>
-      <c r="V25">
-        <v>88.08</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>88.080078125</v>
+      </c>
+      <c r="L25">
+        <v>88.080078125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1463,11 +1442,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>72.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1480,11 +1456,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>72.84999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1516,13 +1489,13 @@
         <v>80.5498046875</v>
       </c>
       <c r="K28">
-        <v>80.5498046875</v>
-      </c>
-      <c r="V28">
-        <v>65.38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>63.780029296875</v>
+      </c>
+      <c r="L28">
+        <v>63.780029296875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1554,13 +1527,13 @@
         <v>75.0498046875</v>
       </c>
       <c r="K29">
-        <v>75.0498046875</v>
-      </c>
-      <c r="V29">
-        <v>98.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>96.27978515625</v>
+      </c>
+      <c r="L29">
+        <v>96.27978515625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1592,13 +1565,13 @@
         <v>73.35009765625</v>
       </c>
       <c r="K30">
-        <v>73.35009765625</v>
-      </c>
-      <c r="V30">
-        <v>104.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>104.68017578125</v>
+      </c>
+      <c r="L30">
+        <v>104.68017578125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1630,13 +1603,13 @@
         <v>74.9501953125</v>
       </c>
       <c r="K31">
-        <v>74.9501953125</v>
-      </c>
-      <c r="V31">
-        <v>90.68000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>90.3798828125</v>
+      </c>
+      <c r="L31">
+        <v>90.3798828125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1668,13 +1641,13 @@
         <v>74.0498046875</v>
       </c>
       <c r="K32">
-        <v>74.0498046875</v>
-      </c>
-      <c r="V32">
-        <v>91.18000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>90.8798828125</v>
+      </c>
+      <c r="L32">
+        <v>90.8798828125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1706,10 +1679,10 @@
         <v>84.85009765625</v>
       </c>
       <c r="K33">
-        <v>84.85009765625</v>
-      </c>
-      <c r="V33">
-        <v>86.36</v>
+        <v>84.56005859375</v>
+      </c>
+      <c r="L33">
+        <v>84.56005859375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -641,6 +641,9 @@
       <c r="L2">
         <v>72.080078125</v>
       </c>
+      <c r="V2">
+        <v>49.17</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -679,6 +682,9 @@
       <c r="L3">
         <v>85.9599609375</v>
       </c>
+      <c r="V3">
+        <v>39.87</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -717,6 +723,9 @@
       <c r="L4">
         <v>91.14013671875</v>
       </c>
+      <c r="V4">
+        <v>48.27</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -755,6 +764,9 @@
       <c r="L5">
         <v>86.0400390625</v>
       </c>
+      <c r="V5">
+        <v>47.79</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -793,6 +805,9 @@
       <c r="L6">
         <v>84.43994140625</v>
       </c>
+      <c r="V6">
+        <v>68.47</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -816,6 +831,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>50.79</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -854,6 +872,9 @@
       <c r="L8">
         <v>85.85009765625</v>
       </c>
+      <c r="V8">
+        <v>59.29</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -892,6 +913,9 @@
       <c r="L9">
         <v>59.010009765625</v>
       </c>
+      <c r="V9">
+        <v>60.57</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -930,6 +954,9 @@
       <c r="L10">
         <v>101.9599609375</v>
       </c>
+      <c r="V10">
+        <v>82.17</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -968,6 +995,9 @@
       <c r="L11">
         <v>77.4501953125</v>
       </c>
+      <c r="V11">
+        <v>59.75</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1006,6 +1036,9 @@
       <c r="L12">
         <v>85.85009765625</v>
       </c>
+      <c r="V12">
+        <v>59.29</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1032,6 +1065,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>43.15</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1043,6 +1079,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>51.19</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1081,6 +1120,9 @@
       <c r="L15">
         <v>71.0498046875</v>
       </c>
+      <c r="V15">
+        <v>57.89</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1110,8 +1152,11 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="V16">
+        <v>39.07</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1142,8 +1187,11 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="V17">
+        <v>84.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1177,8 +1225,11 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="V18">
+        <v>42.07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1215,8 +1266,11 @@
       <c r="L19">
         <v>112.8798828125</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="V19">
+        <v>65.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1253,8 +1307,11 @@
       <c r="L20">
         <v>79.93994140625</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="V20">
+        <v>55.19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1273,8 +1330,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="V21">
+        <v>55.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1311,8 +1371,11 @@
       <c r="L22">
         <v>59.3798828125</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="V22">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1349,8 +1412,11 @@
       <c r="L23">
         <v>93.8798828125</v>
       </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="V23">
+        <v>51.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1387,8 +1453,11 @@
       <c r="L24">
         <v>108.93994140625</v>
       </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="V24">
+        <v>57.09</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1425,8 +1494,11 @@
       <c r="L25">
         <v>88.080078125</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="V25">
+        <v>50.19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1442,8 +1514,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="V26">
+        <v>69.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1456,8 +1531,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="V27">
+        <v>48.85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1494,8 +1572,11 @@
       <c r="L28">
         <v>63.780029296875</v>
       </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="V28">
+        <v>64.69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1532,8 +1613,11 @@
       <c r="L29">
         <v>96.27978515625</v>
       </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="V29">
+        <v>78.89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1570,8 +1654,11 @@
       <c r="L30">
         <v>104.68017578125</v>
       </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="V30">
+        <v>67.29000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1608,8 +1695,11 @@
       <c r="L31">
         <v>90.3798828125</v>
       </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="V31">
+        <v>58.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1646,8 +1736,11 @@
       <c r="L32">
         <v>90.8798828125</v>
       </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="V32">
+        <v>48.77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1683,6 +1776,9 @@
       </c>
       <c r="L33">
         <v>84.56005859375</v>
+      </c>
+      <c r="V33">
+        <v>58.47</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 10</t>
+    <t>Parcial Rodada 11</t>
   </si>
   <si>
     <t>time_id</t>
@@ -639,10 +639,10 @@
         <v>72.080078125</v>
       </c>
       <c r="L2">
-        <v>72.080078125</v>
-      </c>
-      <c r="V2">
-        <v>49.17</v>
+        <v>47.969970703125</v>
+      </c>
+      <c r="M2">
+        <v>47.969970703125</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -680,10 +680,7 @@
         <v>85.9599609375</v>
       </c>
       <c r="L3">
-        <v>85.9599609375</v>
-      </c>
-      <c r="V3">
-        <v>39.87</v>
+        <v>39.469970703125</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -721,10 +718,10 @@
         <v>91.14013671875</v>
       </c>
       <c r="L4">
-        <v>91.14013671875</v>
-      </c>
-      <c r="V4">
-        <v>48.27</v>
+        <v>47.8701171875</v>
+      </c>
+      <c r="M4">
+        <v>47.8701171875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -762,10 +759,7 @@
         <v>86.0400390625</v>
       </c>
       <c r="L5">
-        <v>86.0400390625</v>
-      </c>
-      <c r="V5">
-        <v>47.79</v>
+        <v>46.590087890625</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -803,10 +797,10 @@
         <v>84.43994140625</v>
       </c>
       <c r="L6">
-        <v>84.43994140625</v>
-      </c>
-      <c r="V6">
-        <v>68.47</v>
+        <v>67.27001953125</v>
+      </c>
+      <c r="M6">
+        <v>67.27001953125</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -831,9 +825,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>50.79</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -870,10 +861,10 @@
         <v>85.85009765625</v>
       </c>
       <c r="L8">
-        <v>85.85009765625</v>
-      </c>
-      <c r="V8">
-        <v>59.29</v>
+        <v>58.090087890625</v>
+      </c>
+      <c r="M8">
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -911,10 +902,10 @@
         <v>59.010009765625</v>
       </c>
       <c r="L9">
-        <v>59.010009765625</v>
-      </c>
-      <c r="V9">
-        <v>60.57</v>
+        <v>60.169921875</v>
+      </c>
+      <c r="M9">
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -952,10 +943,10 @@
         <v>101.9599609375</v>
       </c>
       <c r="L10">
-        <v>101.9599609375</v>
-      </c>
-      <c r="V10">
-        <v>82.17</v>
+        <v>82.169921875</v>
+      </c>
+      <c r="M10">
+        <v>82.169921875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -993,10 +984,10 @@
         <v>77.4501953125</v>
       </c>
       <c r="L11">
-        <v>77.4501953125</v>
-      </c>
-      <c r="V11">
-        <v>59.75</v>
+        <v>58.550048828125</v>
+      </c>
+      <c r="M11">
+        <v>58.550048828125</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1034,10 +1025,10 @@
         <v>85.85009765625</v>
       </c>
       <c r="L12">
-        <v>85.85009765625</v>
-      </c>
-      <c r="V12">
-        <v>59.29</v>
+        <v>58.090087890625</v>
+      </c>
+      <c r="M12">
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1065,9 +1056,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>43.15</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1079,9 +1067,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>51.19</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1118,10 +1103,10 @@
         <v>71.0498046875</v>
       </c>
       <c r="L15">
-        <v>71.0498046875</v>
-      </c>
-      <c r="V15">
-        <v>57.89</v>
+        <v>57.489990234375</v>
+      </c>
+      <c r="M15">
+        <v>57.489990234375</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1152,11 +1137,8 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-      <c r="V16">
-        <v>39.07</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1187,11 +1169,8 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-      <c r="V17">
-        <v>84.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1225,11 +1204,8 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-      <c r="V18">
-        <v>42.07</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1264,13 +1240,13 @@
         <v>112.8798828125</v>
       </c>
       <c r="L19">
-        <v>112.8798828125</v>
-      </c>
-      <c r="V19">
-        <v>65.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>64.27001953125</v>
+      </c>
+      <c r="M19">
+        <v>64.27001953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1305,13 +1281,13 @@
         <v>79.93994140625</v>
       </c>
       <c r="L20">
-        <v>79.93994140625</v>
-      </c>
-      <c r="V20">
-        <v>55.19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>54.389892578125</v>
+      </c>
+      <c r="M20">
+        <v>54.389892578125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1330,11 +1306,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>55.12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1369,13 +1342,13 @@
         <v>59.3798828125</v>
       </c>
       <c r="L22">
-        <v>59.3798828125</v>
-      </c>
-      <c r="V22">
-        <v>66.67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>66.27001953125</v>
+      </c>
+      <c r="M22">
+        <v>66.27001953125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1410,13 +1383,13 @@
         <v>93.8798828125</v>
       </c>
       <c r="L23">
-        <v>93.8798828125</v>
-      </c>
-      <c r="V23">
-        <v>51.97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>51.570068359375</v>
+      </c>
+      <c r="M23">
+        <v>51.570068359375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1451,13 +1424,13 @@
         <v>108.93994140625</v>
       </c>
       <c r="L24">
-        <v>108.93994140625</v>
-      </c>
-      <c r="V24">
-        <v>57.09</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>55.889892578125</v>
+      </c>
+      <c r="M24">
+        <v>55.889892578125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1492,13 +1465,13 @@
         <v>88.080078125</v>
       </c>
       <c r="L25">
-        <v>88.080078125</v>
-      </c>
-      <c r="V25">
-        <v>50.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>48.989990234375</v>
+      </c>
+      <c r="M25">
+        <v>48.989990234375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1514,11 +1487,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>69.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1531,11 +1501,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>48.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1570,13 +1537,13 @@
         <v>63.780029296875</v>
       </c>
       <c r="L28">
-        <v>63.780029296875</v>
-      </c>
-      <c r="V28">
-        <v>64.69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>64.2900390625</v>
+      </c>
+      <c r="M28">
+        <v>64.2900390625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1611,13 +1578,13 @@
         <v>96.27978515625</v>
       </c>
       <c r="L29">
-        <v>96.27978515625</v>
-      </c>
-      <c r="V29">
-        <v>78.89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>78.89013671875</v>
+      </c>
+      <c r="M29">
+        <v>78.89013671875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1652,13 +1619,13 @@
         <v>104.68017578125</v>
       </c>
       <c r="L30">
-        <v>104.68017578125</v>
-      </c>
-      <c r="V30">
-        <v>67.29000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>66.89013671875</v>
+      </c>
+      <c r="M30">
+        <v>66.89013671875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1693,13 +1660,13 @@
         <v>90.3798828125</v>
       </c>
       <c r="L31">
-        <v>90.3798828125</v>
-      </c>
-      <c r="V31">
-        <v>58.39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>57.18994140625</v>
+      </c>
+      <c r="M31">
+        <v>57.18994140625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1734,13 +1701,13 @@
         <v>90.8798828125</v>
       </c>
       <c r="L32">
-        <v>90.8798828125</v>
-      </c>
-      <c r="V32">
-        <v>48.77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>47.570068359375</v>
+      </c>
+      <c r="M32">
+        <v>47.570068359375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1775,10 +1742,10 @@
         <v>84.56005859375</v>
       </c>
       <c r="L33">
-        <v>84.56005859375</v>
-      </c>
-      <c r="V33">
-        <v>58.47</v>
+        <v>58.070068359375</v>
+      </c>
+      <c r="M33">
+        <v>58.070068359375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 11</t>
+    <t>Parcial Rodada 12</t>
   </si>
   <si>
     <t>time_id</t>
@@ -642,7 +642,10 @@
         <v>47.969970703125</v>
       </c>
       <c r="M2">
-        <v>47.969970703125</v>
+        <v>87.4599609375</v>
+      </c>
+      <c r="N2">
+        <v>87.4599609375</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -721,7 +724,10 @@
         <v>47.8701171875</v>
       </c>
       <c r="M4">
-        <v>47.8701171875</v>
+        <v>83.47998046875</v>
+      </c>
+      <c r="N4">
+        <v>83.47998046875</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -800,7 +806,10 @@
         <v>67.27001953125</v>
       </c>
       <c r="M6">
-        <v>67.27001953125</v>
+        <v>94.06005859375</v>
+      </c>
+      <c r="N6">
+        <v>94.06005859375</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -864,7 +873,10 @@
         <v>58.090087890625</v>
       </c>
       <c r="M8">
-        <v>58.090087890625</v>
+        <v>88.759765625</v>
+      </c>
+      <c r="N8">
+        <v>88.759765625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -905,7 +917,10 @@
         <v>60.169921875</v>
       </c>
       <c r="M9">
-        <v>60.169921875</v>
+        <v>82.81005859375</v>
+      </c>
+      <c r="N9">
+        <v>82.81005859375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -946,7 +961,10 @@
         <v>82.169921875</v>
       </c>
       <c r="M10">
-        <v>82.169921875</v>
+        <v>101.35986328125</v>
+      </c>
+      <c r="N10">
+        <v>101.35986328125</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -987,7 +1005,10 @@
         <v>58.550048828125</v>
       </c>
       <c r="M11">
-        <v>58.550048828125</v>
+        <v>89.080078125</v>
+      </c>
+      <c r="N11">
+        <v>89.080078125</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1028,7 +1049,10 @@
         <v>58.090087890625</v>
       </c>
       <c r="M12">
-        <v>58.090087890625</v>
+        <v>79.66015625</v>
+      </c>
+      <c r="N12">
+        <v>79.66015625</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1106,7 +1130,7 @@
         <v>57.489990234375</v>
       </c>
       <c r="M15">
-        <v>57.489990234375</v>
+        <v>70.16015625</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1138,7 +1162,7 @@
         <v>49.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1170,7 +1194,7 @@
         <v>45.699951171875</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1205,7 +1229,7 @@
         <v>56.090087890625</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1243,10 +1267,13 @@
         <v>64.27001953125</v>
       </c>
       <c r="M19">
-        <v>64.27001953125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>103.66015625</v>
+      </c>
+      <c r="N19">
+        <v>103.66015625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1284,10 +1311,13 @@
         <v>54.389892578125</v>
       </c>
       <c r="M20">
-        <v>54.389892578125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>91.27978515625</v>
+      </c>
+      <c r="N20">
+        <v>91.27978515625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1307,7 +1337,7 @@
         <v>27.4300537109375</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1345,10 +1375,13 @@
         <v>66.27001953125</v>
       </c>
       <c r="M22">
-        <v>66.27001953125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>105.9599609375</v>
+      </c>
+      <c r="N22">
+        <v>105.9599609375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1386,10 +1419,13 @@
         <v>51.570068359375</v>
       </c>
       <c r="M23">
-        <v>51.570068359375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>79.580078125</v>
+      </c>
+      <c r="N23">
+        <v>79.580078125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1427,10 +1463,13 @@
         <v>55.889892578125</v>
       </c>
       <c r="M24">
-        <v>55.889892578125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>91.9599609375</v>
+      </c>
+      <c r="N24">
+        <v>91.9599609375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1468,10 +1507,13 @@
         <v>48.989990234375</v>
       </c>
       <c r="M25">
-        <v>48.989990234375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>97.16015625</v>
+      </c>
+      <c r="N25">
+        <v>97.16015625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1488,7 +1530,7 @@
         <v>65.259765625</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:14">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1502,7 +1544,7 @@
         <v>36.429931640625</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:14">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1540,10 +1582,13 @@
         <v>64.2900390625</v>
       </c>
       <c r="M28">
-        <v>64.2900390625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>81.759765625</v>
+      </c>
+      <c r="N28">
+        <v>81.759765625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1581,10 +1626,13 @@
         <v>78.89013671875</v>
       </c>
       <c r="M29">
-        <v>78.89013671875</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>86.66015625</v>
+      </c>
+      <c r="N29">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1622,10 +1670,13 @@
         <v>66.89013671875</v>
       </c>
       <c r="M30">
-        <v>66.89013671875</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>90.4599609375</v>
+      </c>
+      <c r="N30">
+        <v>90.4599609375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1663,10 +1714,13 @@
         <v>57.18994140625</v>
       </c>
       <c r="M31">
-        <v>57.18994140625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>86.259765625</v>
+      </c>
+      <c r="N31">
+        <v>86.259765625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1704,10 +1758,10 @@
         <v>47.570068359375</v>
       </c>
       <c r="M32">
-        <v>47.570068359375</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1745,7 +1799,10 @@
         <v>58.070068359375</v>
       </c>
       <c r="M33">
-        <v>58.070068359375</v>
+        <v>92.56005859375</v>
+      </c>
+      <c r="N33">
+        <v>92.56005859375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -647,6 +647,9 @@
       <c r="N2">
         <v>87.4599609375</v>
       </c>
+      <c r="V2">
+        <v>69.8</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -685,6 +688,9 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
+      <c r="V3">
+        <v>81.45</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -729,6 +735,9 @@
       <c r="N4">
         <v>83.47998046875</v>
       </c>
+      <c r="V4">
+        <v>63.8</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -767,6 +776,9 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
+      <c r="V5">
+        <v>90.55</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -811,6 +823,9 @@
       <c r="N6">
         <v>94.06005859375</v>
       </c>
+      <c r="V6">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -834,6 +849,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>75.91</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -878,6 +896,9 @@
       <c r="N8">
         <v>88.759765625</v>
       </c>
+      <c r="V8">
+        <v>86.66</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -922,6 +943,9 @@
       <c r="N9">
         <v>82.81005859375</v>
       </c>
+      <c r="V9">
+        <v>77.34999999999999</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -966,6 +990,9 @@
       <c r="N10">
         <v>101.35986328125</v>
       </c>
+      <c r="V10">
+        <v>64.2</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -1010,6 +1037,9 @@
       <c r="N11">
         <v>89.080078125</v>
       </c>
+      <c r="V11">
+        <v>92.09999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1054,6 +1084,9 @@
       <c r="N12">
         <v>79.66015625</v>
       </c>
+      <c r="V12">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1080,6 +1113,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>44.35</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1091,6 +1127,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>63.95</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1132,6 +1171,9 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
+      <c r="V15">
+        <v>83.7</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1161,8 +1203,11 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="V16">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1193,8 +1238,11 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="V17">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1228,8 +1276,11 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="V18">
+        <v>92.34999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1272,8 +1323,11 @@
       <c r="N19">
         <v>103.66015625</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="V19">
+        <v>77.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1316,8 +1370,11 @@
       <c r="N20">
         <v>91.27978515625</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="V20">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1336,8 +1393,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="V21">
+        <v>69.31999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1380,8 +1440,11 @@
       <c r="N22">
         <v>105.9599609375</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="V22">
+        <v>77.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1424,8 +1487,11 @@
       <c r="N23">
         <v>79.580078125</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="V23">
+        <v>77.95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1468,8 +1534,11 @@
       <c r="N24">
         <v>91.9599609375</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="V24">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1512,8 +1581,11 @@
       <c r="N25">
         <v>97.16015625</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="V25">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1529,8 +1601,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="V26">
+        <v>82.15000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1543,8 +1618,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="V27">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1587,8 +1665,11 @@
       <c r="N28">
         <v>81.759765625</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="V28">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1631,8 +1712,11 @@
       <c r="N29">
         <v>86.66015625</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="V29">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1675,8 +1759,11 @@
       <c r="N30">
         <v>90.4599609375</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="V30">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1719,8 +1806,11 @@
       <c r="N31">
         <v>86.259765625</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="V31">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1760,8 +1850,11 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="V32">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1803,6 +1896,9 @@
       </c>
       <c r="N33">
         <v>92.56005859375</v>
+      </c>
+      <c r="V33">
+        <v>70.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 12</t>
+    <t>Parcial Rodada 13</t>
   </si>
   <si>
     <t>time_id</t>
@@ -645,10 +645,10 @@
         <v>87.4599609375</v>
       </c>
       <c r="N2">
-        <v>87.4599609375</v>
-      </c>
-      <c r="V2">
-        <v>69.8</v>
+        <v>69.7998046875</v>
+      </c>
+      <c r="O2">
+        <v>69.7998046875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -688,9 +688,6 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
-      <c r="V3">
-        <v>81.45</v>
-      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -733,10 +730,10 @@
         <v>83.47998046875</v>
       </c>
       <c r="N4">
-        <v>83.47998046875</v>
-      </c>
-      <c r="V4">
-        <v>63.8</v>
+        <v>63.800048828125</v>
+      </c>
+      <c r="O4">
+        <v>63.800048828125</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -776,9 +773,6 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
-      <c r="V5">
-        <v>90.55</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -821,9 +815,9 @@
         <v>94.06005859375</v>
       </c>
       <c r="N6">
-        <v>94.06005859375</v>
-      </c>
-      <c r="V6">
+        <v>84.5</v>
+      </c>
+      <c r="O6">
         <v>84.5</v>
       </c>
     </row>
@@ -849,9 +843,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>75.91</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -894,10 +885,10 @@
         <v>88.759765625</v>
       </c>
       <c r="N8">
-        <v>88.759765625</v>
-      </c>
-      <c r="V8">
-        <v>86.66</v>
+        <v>86.66015625</v>
+      </c>
+      <c r="O8">
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -941,10 +932,10 @@
         <v>82.81005859375</v>
       </c>
       <c r="N9">
-        <v>82.81005859375</v>
-      </c>
-      <c r="V9">
-        <v>77.34999999999999</v>
+        <v>77.35009765625</v>
+      </c>
+      <c r="O9">
+        <v>77.35009765625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -988,10 +979,10 @@
         <v>101.35986328125</v>
       </c>
       <c r="N10">
-        <v>101.35986328125</v>
-      </c>
-      <c r="V10">
-        <v>64.2</v>
+        <v>64.2001953125</v>
+      </c>
+      <c r="O10">
+        <v>64.2001953125</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1035,10 +1026,10 @@
         <v>89.080078125</v>
       </c>
       <c r="N11">
-        <v>89.080078125</v>
-      </c>
-      <c r="V11">
-        <v>92.09999999999999</v>
+        <v>92.10009765625</v>
+      </c>
+      <c r="O11">
+        <v>92.10009765625</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1082,10 +1073,10 @@
         <v>79.66015625</v>
       </c>
       <c r="N12">
-        <v>79.66015625</v>
-      </c>
-      <c r="V12">
-        <v>84.40000000000001</v>
+        <v>84.39990234375</v>
+      </c>
+      <c r="O12">
+        <v>84.39990234375</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1113,9 +1104,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>44.35</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1127,9 +1115,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>63.95</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1171,9 +1156,6 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
-      <c r="V15">
-        <v>83.7</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1203,11 +1185,8 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-      <c r="V16">
-        <v>84.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1238,11 +1217,8 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-      <c r="V17">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1276,11 +1252,8 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-      <c r="V18">
-        <v>92.34999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1321,13 +1294,13 @@
         <v>103.66015625</v>
       </c>
       <c r="N19">
-        <v>103.66015625</v>
-      </c>
-      <c r="V19">
-        <v>77.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>77.9501953125</v>
+      </c>
+      <c r="O19">
+        <v>77.9501953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1368,13 +1341,13 @@
         <v>91.27978515625</v>
       </c>
       <c r="N20">
-        <v>91.27978515625</v>
-      </c>
-      <c r="V20">
-        <v>81.09999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>81.10009765625</v>
+      </c>
+      <c r="O20">
+        <v>81.10009765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1393,11 +1366,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>69.31999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1438,13 +1408,13 @@
         <v>105.9599609375</v>
       </c>
       <c r="N22">
-        <v>105.9599609375</v>
-      </c>
-      <c r="V22">
         <v>77.25</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="O22">
+        <v>77.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1485,13 +1455,13 @@
         <v>79.580078125</v>
       </c>
       <c r="N23">
-        <v>79.580078125</v>
-      </c>
-      <c r="V23">
-        <v>77.95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>77.9501953125</v>
+      </c>
+      <c r="O23">
+        <v>77.9501953125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1532,13 +1502,10 @@
         <v>91.9599609375</v>
       </c>
       <c r="N24">
-        <v>91.9599609375</v>
-      </c>
-      <c r="V24">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>61.39990234375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1579,13 +1546,10 @@
         <v>97.16015625</v>
       </c>
       <c r="N25">
-        <v>97.16015625</v>
-      </c>
-      <c r="V25">
-        <v>54.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>54.60009765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1601,11 +1565,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>82.15000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1618,11 +1579,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1663,13 +1621,13 @@
         <v>81.759765625</v>
       </c>
       <c r="N28">
-        <v>81.759765625</v>
-      </c>
-      <c r="V28">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>74.39990234375</v>
+      </c>
+      <c r="O28">
+        <v>74.39990234375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1710,13 +1668,13 @@
         <v>86.66015625</v>
       </c>
       <c r="N29">
-        <v>86.66015625</v>
-      </c>
-      <c r="V29">
-        <v>80.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>80.7001953125</v>
+      </c>
+      <c r="O29">
+        <v>80.7001953125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1757,13 +1715,13 @@
         <v>90.4599609375</v>
       </c>
       <c r="N30">
-        <v>90.4599609375</v>
-      </c>
-      <c r="V30">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>84.39990234375</v>
+      </c>
+      <c r="O30">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1806,11 +1764,11 @@
       <c r="N31">
         <v>86.259765625</v>
       </c>
-      <c r="V31">
-        <v>82.90000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="O31">
+        <v>82.89990234375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1850,11 +1808,8 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-      <c r="V32">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1895,10 +1850,10 @@
         <v>92.56005859375</v>
       </c>
       <c r="N33">
-        <v>92.56005859375</v>
-      </c>
-      <c r="V33">
-        <v>70.59999999999999</v>
+        <v>70.60009765625</v>
+      </c>
+      <c r="O33">
+        <v>70.60009765625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -650,6 +650,9 @@
       <c r="O2">
         <v>69.7998046875</v>
       </c>
+      <c r="V2">
+        <v>112.02</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -688,6 +691,9 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
+      <c r="V3">
+        <v>113.22</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -735,6 +741,9 @@
       <c r="O4">
         <v>63.800048828125</v>
       </c>
+      <c r="V4">
+        <v>110.35</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -773,6 +782,9 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
+      <c r="V5">
+        <v>120.02</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -820,6 +832,9 @@
       <c r="O6">
         <v>84.5</v>
       </c>
+      <c r="V6">
+        <v>87.92</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -843,6 +858,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>80.12</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -890,6 +908,9 @@
       <c r="O8">
         <v>86.66015625</v>
       </c>
+      <c r="V8">
+        <v>97.62</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -937,6 +958,9 @@
       <c r="O9">
         <v>77.35009765625</v>
       </c>
+      <c r="V9">
+        <v>91.87</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -984,6 +1008,9 @@
       <c r="O10">
         <v>64.2001953125</v>
       </c>
+      <c r="V10">
+        <v>113.02</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -1031,6 +1058,9 @@
       <c r="O11">
         <v>92.10009765625</v>
       </c>
+      <c r="V11">
+        <v>74.37</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1078,6 +1108,9 @@
       <c r="O12">
         <v>84.39990234375</v>
       </c>
+      <c r="V12">
+        <v>97.62</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1104,6 +1137,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>39.7</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1115,6 +1151,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>89.42</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1156,6 +1195,9 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
+      <c r="V15">
+        <v>92.62</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1185,8 +1227,11 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="V16">
+        <v>105.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1217,8 +1262,11 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="V17">
+        <v>71.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1252,8 +1300,11 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="V18">
+        <v>98.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1299,8 +1350,11 @@
       <c r="O19">
         <v>77.9501953125</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="V19">
+        <v>117.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1346,8 +1400,11 @@
       <c r="O20">
         <v>81.10009765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="V20">
+        <v>136.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1366,8 +1423,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="V21">
+        <v>57.96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1413,8 +1473,11 @@
       <c r="O22">
         <v>77.25</v>
       </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="V22">
+        <v>98.37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1460,8 +1523,11 @@
       <c r="O23">
         <v>77.9501953125</v>
       </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="V23">
+        <v>111.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1504,8 +1570,11 @@
       <c r="N24">
         <v>61.39990234375</v>
       </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="V24">
+        <v>102.32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1548,8 +1617,11 @@
       <c r="N25">
         <v>54.60009765625</v>
       </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="V25">
+        <v>101.87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1565,8 +1637,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="V26">
+        <v>101.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1579,8 +1654,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="V27">
+        <v>53.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1626,8 +1704,11 @@
       <c r="O28">
         <v>74.39990234375</v>
       </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="V28">
+        <v>105.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1673,8 +1754,11 @@
       <c r="O29">
         <v>80.7001953125</v>
       </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="V29">
+        <v>108.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1720,8 +1804,11 @@
       <c r="O30">
         <v>84.39990234375</v>
       </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="V30">
+        <v>108.52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1762,13 +1849,16 @@
         <v>86.259765625</v>
       </c>
       <c r="N31">
-        <v>86.259765625</v>
+        <v>82.89990234375</v>
       </c>
       <c r="O31">
         <v>82.89990234375</v>
       </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="V31">
+        <v>95.02</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1808,8 +1898,11 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="V32">
+        <v>93.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1854,6 +1947,9 @@
       </c>
       <c r="O33">
         <v>70.60009765625</v>
+      </c>
+      <c r="V33">
+        <v>94.47</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -651,7 +651,7 @@
         <v>69.7998046875</v>
       </c>
       <c r="V2">
-        <v>112.02</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -692,7 +692,7 @@
         <v>39.469970703125</v>
       </c>
       <c r="V3">
-        <v>113.22</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -783,7 +783,7 @@
         <v>46.590087890625</v>
       </c>
       <c r="V5">
-        <v>120.02</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -833,7 +833,7 @@
         <v>84.5</v>
       </c>
       <c r="V6">
-        <v>87.92</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -859,7 +859,7 @@
         <v>69.3701171875</v>
       </c>
       <c r="V7">
-        <v>80.12</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -909,7 +909,7 @@
         <v>86.66015625</v>
       </c>
       <c r="V8">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -959,7 +959,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="V9">
-        <v>91.87</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1009,7 +1009,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="V10">
-        <v>113.02</v>
+        <v>121.09</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1059,7 +1059,7 @@
         <v>92.10009765625</v>
       </c>
       <c r="V11">
-        <v>74.37</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1109,7 +1109,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="V12">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1152,7 +1152,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="V14">
-        <v>89.42</v>
+        <v>104.89</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1196,7 +1196,7 @@
         <v>70.16015625</v>
       </c>
       <c r="V15">
-        <v>92.62</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1228,7 +1228,7 @@
         <v>49.469970703125</v>
       </c>
       <c r="V16">
-        <v>105.12</v>
+        <v>117.04</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1263,7 +1263,7 @@
         <v>45.699951171875</v>
       </c>
       <c r="V17">
-        <v>71.95</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1301,7 +1301,7 @@
         <v>56.090087890625</v>
       </c>
       <c r="V18">
-        <v>98.12</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1351,7 +1351,7 @@
         <v>77.9501953125</v>
       </c>
       <c r="V19">
-        <v>117.22</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1401,7 +1401,7 @@
         <v>81.10009765625</v>
       </c>
       <c r="V20">
-        <v>136.52</v>
+        <v>136.59</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1474,7 +1474,7 @@
         <v>77.25</v>
       </c>
       <c r="V22">
-        <v>98.37</v>
+        <v>122.49</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -1524,7 +1524,7 @@
         <v>77.9501953125</v>
       </c>
       <c r="V23">
-        <v>111.22</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1571,7 +1571,7 @@
         <v>61.39990234375</v>
       </c>
       <c r="V24">
-        <v>102.32</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1618,7 +1618,7 @@
         <v>54.60009765625</v>
       </c>
       <c r="V25">
-        <v>101.87</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1638,7 +1638,7 @@
         <v>65.259765625</v>
       </c>
       <c r="V26">
-        <v>101.07</v>
+        <v>128.44</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -1705,7 +1705,7 @@
         <v>74.39990234375</v>
       </c>
       <c r="V28">
-        <v>105.72</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -1755,7 +1755,7 @@
         <v>80.7001953125</v>
       </c>
       <c r="V29">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -1805,7 +1805,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="V30">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -1855,7 +1855,7 @@
         <v>82.89990234375</v>
       </c>
       <c r="V31">
-        <v>95.02</v>
+        <v>104.29</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -1899,7 +1899,7 @@
         <v>69.25</v>
       </c>
       <c r="V32">
-        <v>93.92</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1949,7 +1949,7 @@
         <v>70.60009765625</v>
       </c>
       <c r="V33">
-        <v>94.47</v>
+        <v>117.54</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 13</t>
+    <t>Parcial Rodada 14</t>
   </si>
   <si>
     <t>time_id</t>
@@ -648,10 +648,10 @@
         <v>69.7998046875</v>
       </c>
       <c r="O2">
-        <v>69.7998046875</v>
-      </c>
-      <c r="V2">
-        <v>120.79</v>
+        <v>120.7900390625</v>
+      </c>
+      <c r="P2">
+        <v>120.7900390625</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -691,9 +691,6 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
-      <c r="V3">
-        <v>113.29</v>
-      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -739,10 +736,10 @@
         <v>63.800048828125</v>
       </c>
       <c r="O4">
-        <v>63.800048828125</v>
-      </c>
-      <c r="V4">
-        <v>110.35</v>
+        <v>110.35009765625</v>
+      </c>
+      <c r="P4">
+        <v>110.35009765625</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -782,9 +779,6 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
-      <c r="V5">
-        <v>120.79</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -830,10 +824,7 @@
         <v>84.5</v>
       </c>
       <c r="O6">
-        <v>84.5</v>
-      </c>
-      <c r="V6">
-        <v>97.79000000000001</v>
+        <v>97.7900390625</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -858,9 +849,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>80.19</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -906,10 +894,10 @@
         <v>86.66015625</v>
       </c>
       <c r="O8">
-        <v>86.66015625</v>
-      </c>
-      <c r="V8">
-        <v>106.39</v>
+        <v>106.39013671875</v>
+      </c>
+      <c r="P8">
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -956,10 +944,10 @@
         <v>77.35009765625</v>
       </c>
       <c r="O9">
-        <v>77.35009765625</v>
-      </c>
-      <c r="V9">
-        <v>115.44</v>
+        <v>115.43994140625</v>
+      </c>
+      <c r="P9">
+        <v>115.43994140625</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1006,10 +994,10 @@
         <v>64.2001953125</v>
       </c>
       <c r="O10">
-        <v>64.2001953125</v>
-      </c>
-      <c r="V10">
-        <v>121.09</v>
+        <v>121.08984375</v>
+      </c>
+      <c r="P10">
+        <v>121.08984375</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1056,10 +1044,7 @@
         <v>92.10009765625</v>
       </c>
       <c r="O11">
-        <v>92.10009765625</v>
-      </c>
-      <c r="V11">
-        <v>74.44</v>
+        <v>74.43994140625</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1106,10 +1091,10 @@
         <v>84.39990234375</v>
       </c>
       <c r="O12">
-        <v>84.39990234375</v>
-      </c>
-      <c r="V12">
-        <v>106.39</v>
+        <v>106.39013671875</v>
+      </c>
+      <c r="P12">
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1137,9 +1122,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>39.7</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1151,9 +1133,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>104.89</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1195,9 +1174,6 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
-      <c r="V15">
-        <v>93.89</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1227,11 +1203,8 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-      <c r="V16">
-        <v>117.04</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1262,11 +1235,8 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-      <c r="V17">
-        <v>90.15000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1300,11 +1270,8 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-      <c r="V18">
-        <v>97.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1348,13 +1315,13 @@
         <v>77.9501953125</v>
       </c>
       <c r="O19">
-        <v>77.9501953125</v>
-      </c>
-      <c r="V19">
-        <v>116.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>116.7900390625</v>
+      </c>
+      <c r="P19">
+        <v>116.7900390625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1398,13 +1365,13 @@
         <v>81.10009765625</v>
       </c>
       <c r="O20">
-        <v>81.10009765625</v>
-      </c>
-      <c r="V20">
-        <v>136.59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>136.58984375</v>
+      </c>
+      <c r="P20">
+        <v>136.58984375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1423,11 +1390,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>57.96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1471,13 +1435,13 @@
         <v>77.25</v>
       </c>
       <c r="O22">
-        <v>77.25</v>
-      </c>
-      <c r="V22">
-        <v>122.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>122.490234375</v>
+      </c>
+      <c r="P22">
+        <v>122.490234375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1521,13 +1485,13 @@
         <v>77.9501953125</v>
       </c>
       <c r="O23">
-        <v>77.9501953125</v>
-      </c>
-      <c r="V23">
-        <v>111.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>111.2900390625</v>
+      </c>
+      <c r="P23">
+        <v>111.2900390625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1570,11 +1534,8 @@
       <c r="N24">
         <v>61.39990234375</v>
       </c>
-      <c r="V24">
-        <v>103.59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1617,11 +1578,8 @@
       <c r="N25">
         <v>54.60009765625</v>
       </c>
-      <c r="V25">
-        <v>103.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1637,11 +1595,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>128.44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1654,11 +1609,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>53.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1702,13 +1654,13 @@
         <v>74.39990234375</v>
       </c>
       <c r="O28">
-        <v>74.39990234375</v>
-      </c>
-      <c r="V28">
-        <v>113.79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>113.7900390625</v>
+      </c>
+      <c r="P28">
+        <v>113.7900390625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1752,13 +1704,13 @@
         <v>80.7001953125</v>
       </c>
       <c r="O29">
-        <v>80.7001953125</v>
-      </c>
-      <c r="V29">
-        <v>108.59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>108.58984375</v>
+      </c>
+      <c r="P29">
+        <v>108.58984375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1802,13 +1754,13 @@
         <v>84.39990234375</v>
       </c>
       <c r="O30">
-        <v>84.39990234375</v>
-      </c>
-      <c r="V30">
-        <v>108.59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>108.58984375</v>
+      </c>
+      <c r="P30">
+        <v>108.58984375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1852,13 +1804,13 @@
         <v>82.89990234375</v>
       </c>
       <c r="O31">
-        <v>82.89990234375</v>
-      </c>
-      <c r="V31">
-        <v>104.29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>104.2900390625</v>
+      </c>
+      <c r="P31">
+        <v>104.2900390625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1898,11 +1850,8 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-      <c r="V32">
-        <v>101.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1946,10 +1895,10 @@
         <v>70.60009765625</v>
       </c>
       <c r="O33">
-        <v>70.60009765625</v>
-      </c>
-      <c r="V33">
-        <v>117.54</v>
+        <v>117.5400390625</v>
+      </c>
+      <c r="P33">
+        <v>117.5400390625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 14</t>
+    <t>Parcial Rodada 15</t>
   </si>
   <si>
     <t>time_id</t>
@@ -651,7 +651,7 @@
         <v>120.7900390625</v>
       </c>
       <c r="P2">
-        <v>120.7900390625</v>
+        <v>41.949951171875</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -739,7 +739,10 @@
         <v>110.35009765625</v>
       </c>
       <c r="P4">
-        <v>110.35009765625</v>
+        <v>51.080078125</v>
+      </c>
+      <c r="Q4">
+        <v>51.080078125</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -897,7 +900,10 @@
         <v>106.39013671875</v>
       </c>
       <c r="P8">
-        <v>106.39013671875</v>
+        <v>53.780029296875</v>
+      </c>
+      <c r="Q8">
+        <v>53.780029296875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -947,7 +953,10 @@
         <v>115.43994140625</v>
       </c>
       <c r="P9">
-        <v>115.43994140625</v>
+        <v>57.72998046875</v>
+      </c>
+      <c r="Q9">
+        <v>57.72998046875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -997,7 +1006,10 @@
         <v>121.08984375</v>
       </c>
       <c r="P10">
-        <v>121.08984375</v>
+        <v>78.35009765625</v>
+      </c>
+      <c r="Q10">
+        <v>78.35009765625</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1094,7 +1106,10 @@
         <v>106.39013671875</v>
       </c>
       <c r="P12">
-        <v>106.39013671875</v>
+        <v>51.8798828125</v>
+      </c>
+      <c r="Q12">
+        <v>51.8798828125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1204,7 +1219,7 @@
         <v>49.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1236,7 +1251,7 @@
         <v>45.699951171875</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:17">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1271,7 +1286,7 @@
         <v>56.090087890625</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1318,10 +1333,13 @@
         <v>116.7900390625</v>
       </c>
       <c r="P19">
-        <v>116.7900390625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>76.47998046875</v>
+      </c>
+      <c r="Q19">
+        <v>76.47998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1368,10 +1386,10 @@
         <v>136.58984375</v>
       </c>
       <c r="P20">
-        <v>136.58984375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>46.050048828125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1391,7 +1409,7 @@
         <v>27.4300537109375</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1438,10 +1456,13 @@
         <v>122.490234375</v>
       </c>
       <c r="P22">
-        <v>122.490234375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+        <v>53.47998046875</v>
+      </c>
+      <c r="Q22">
+        <v>53.47998046875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1488,10 +1509,13 @@
         <v>111.2900390625</v>
       </c>
       <c r="P23">
-        <v>111.2900390625</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>47.050048828125</v>
+      </c>
+      <c r="Q23">
+        <v>47.050048828125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1535,7 +1559,7 @@
         <v>61.39990234375</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1579,7 +1603,7 @@
         <v>54.60009765625</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:17">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1596,7 +1620,7 @@
         <v>65.259765625</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:17">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1610,7 +1634,7 @@
         <v>36.429931640625</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:17">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1657,10 +1681,13 @@
         <v>113.7900390625</v>
       </c>
       <c r="P28">
-        <v>113.7900390625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+        <v>76.9501953125</v>
+      </c>
+      <c r="Q28">
+        <v>76.9501953125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1707,10 +1734,13 @@
         <v>108.58984375</v>
       </c>
       <c r="P29">
-        <v>108.58984375</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>61.679931640625</v>
+      </c>
+      <c r="Q29">
+        <v>61.679931640625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1757,10 +1787,13 @@
         <v>108.58984375</v>
       </c>
       <c r="P30">
-        <v>108.58984375</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>49.280029296875</v>
+      </c>
+      <c r="Q30">
+        <v>49.280029296875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1807,10 +1840,13 @@
         <v>104.2900390625</v>
       </c>
       <c r="P31">
-        <v>104.2900390625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+        <v>48.080078125</v>
+      </c>
+      <c r="Q31">
+        <v>48.080078125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1851,7 +1887,7 @@
         <v>69.25</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:17">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1898,7 +1934,10 @@
         <v>117.5400390625</v>
       </c>
       <c r="P33">
-        <v>117.5400390625</v>
+        <v>53.139892578125</v>
+      </c>
+      <c r="Q33">
+        <v>53.139892578125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -653,6 +653,9 @@
       <c r="P2">
         <v>41.949951171875</v>
       </c>
+      <c r="V2">
+        <v>53.02</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -691,6 +694,9 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
+      <c r="V3">
+        <v>60.17</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -744,6 +750,9 @@
       <c r="Q4">
         <v>51.080078125</v>
       </c>
+      <c r="V4">
+        <v>65.59999999999999</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -782,6 +791,9 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
+      <c r="V5">
+        <v>50.25</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -829,6 +841,9 @@
       <c r="O6">
         <v>97.7900390625</v>
       </c>
+      <c r="V6">
+        <v>58.27</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -852,6 +867,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>51.93</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -905,6 +923,9 @@
       <c r="Q8">
         <v>53.780029296875</v>
       </c>
+      <c r="V8">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -958,6 +979,9 @@
       <c r="Q9">
         <v>57.72998046875</v>
       </c>
+      <c r="V9">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -1011,6 +1035,9 @@
       <c r="Q10">
         <v>78.35009765625</v>
       </c>
+      <c r="V10">
+        <v>50.63</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -1058,6 +1085,9 @@
       <c r="O11">
         <v>74.43994140625</v>
       </c>
+      <c r="V11">
+        <v>46.17</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1111,6 +1141,9 @@
       <c r="Q12">
         <v>51.8798828125</v>
       </c>
+      <c r="V12">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1137,6 +1170,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>52.43</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1148,6 +1184,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>67.65000000000001</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1189,6 +1228,9 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
+      <c r="V15">
+        <v>42.25</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1218,8 +1260,11 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="V16">
+        <v>55.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1250,8 +1295,11 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="V17">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1285,8 +1333,11 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="V18">
+        <v>65.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1338,8 +1389,11 @@
       <c r="Q19">
         <v>76.47998046875</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="V19">
+        <v>43.73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1388,8 +1442,11 @@
       <c r="P20">
         <v>46.050048828125</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="V20">
+        <v>48.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1408,8 +1465,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="V21">
+        <v>31.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1461,8 +1521,11 @@
       <c r="Q22">
         <v>53.47998046875</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="V22">
+        <v>68.34999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1514,8 +1577,11 @@
       <c r="Q23">
         <v>47.050048828125</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="V23">
+        <v>51.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1558,8 +1624,11 @@
       <c r="N24">
         <v>61.39990234375</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="V24">
+        <v>67.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1602,8 +1671,11 @@
       <c r="N25">
         <v>54.60009765625</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="V25">
+        <v>30.65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1619,8 +1691,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="V26">
+        <v>24.42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1633,8 +1708,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="V27">
+        <v>40.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1686,8 +1764,11 @@
       <c r="Q28">
         <v>76.9501953125</v>
       </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="V28">
+        <v>61.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1739,8 +1820,11 @@
       <c r="Q29">
         <v>61.679931640625</v>
       </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="V29">
+        <v>49.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1792,8 +1876,11 @@
       <c r="Q30">
         <v>49.280029296875</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="V30">
+        <v>54.58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1845,8 +1932,11 @@
       <c r="Q31">
         <v>48.080078125</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="V31">
+        <v>64.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1886,8 +1976,11 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="V32">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1938,6 +2031,9 @@
       </c>
       <c r="Q33">
         <v>53.139892578125</v>
+      </c>
+      <c r="V33">
+        <v>39.22</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 15</t>
+    <t>Parcial Rodada 16</t>
   </si>
   <si>
     <t>time_id</t>
@@ -653,9 +653,6 @@
       <c r="P2">
         <v>41.949951171875</v>
       </c>
-      <c r="V2">
-        <v>53.02</v>
-      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -694,9 +691,6 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
-      <c r="V3">
-        <v>60.17</v>
-      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -748,10 +742,10 @@
         <v>51.080078125</v>
       </c>
       <c r="Q4">
-        <v>51.080078125</v>
-      </c>
-      <c r="V4">
-        <v>65.59999999999999</v>
+        <v>65.60009765625</v>
+      </c>
+      <c r="R4">
+        <v>65.60009765625</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -791,9 +785,6 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
-      <c r="V5">
-        <v>50.25</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -841,9 +832,6 @@
       <c r="O6">
         <v>97.7900390625</v>
       </c>
-      <c r="V6">
-        <v>58.27</v>
-      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -867,9 +855,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>51.93</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -921,9 +906,9 @@
         <v>53.780029296875</v>
       </c>
       <c r="Q8">
-        <v>53.780029296875</v>
-      </c>
-      <c r="V8">
+        <v>63.75</v>
+      </c>
+      <c r="R8">
         <v>63.75</v>
       </c>
     </row>
@@ -977,10 +962,10 @@
         <v>57.72998046875</v>
       </c>
       <c r="Q9">
-        <v>57.72998046875</v>
-      </c>
-      <c r="V9">
-        <v>55.9</v>
+        <v>55.89990234375</v>
+      </c>
+      <c r="R9">
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1033,10 +1018,10 @@
         <v>78.35009765625</v>
       </c>
       <c r="Q10">
-        <v>78.35009765625</v>
-      </c>
-      <c r="V10">
-        <v>50.63</v>
+        <v>50.6298828125</v>
+      </c>
+      <c r="R10">
+        <v>50.6298828125</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1085,9 +1070,6 @@
       <c r="O11">
         <v>74.43994140625</v>
       </c>
-      <c r="V11">
-        <v>46.17</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1139,9 +1121,9 @@
         <v>51.8798828125</v>
       </c>
       <c r="Q12">
-        <v>51.8798828125</v>
-      </c>
-      <c r="V12">
+        <v>63.75</v>
+      </c>
+      <c r="R12">
         <v>63.75</v>
       </c>
     </row>
@@ -1170,9 +1152,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>52.43</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1184,9 +1163,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>67.65000000000001</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1228,9 +1204,6 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
-      <c r="V15">
-        <v>42.25</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1260,11 +1233,8 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-      <c r="V16">
-        <v>55.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1295,11 +1265,8 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-      <c r="V17">
-        <v>53.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1333,11 +1300,8 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-      <c r="V18">
-        <v>65.34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1387,13 +1351,10 @@
         <v>76.47998046875</v>
       </c>
       <c r="Q19">
-        <v>76.47998046875</v>
-      </c>
-      <c r="V19">
-        <v>43.73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>43.72998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1442,11 +1403,8 @@
       <c r="P20">
         <v>46.050048828125</v>
       </c>
-      <c r="V20">
-        <v>48.27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1465,11 +1423,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>31.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1519,13 +1474,13 @@
         <v>53.47998046875</v>
       </c>
       <c r="Q22">
-        <v>53.47998046875</v>
-      </c>
-      <c r="V22">
-        <v>68.34999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>68.35009765625</v>
+      </c>
+      <c r="R22">
+        <v>68.35009765625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1575,13 +1530,13 @@
         <v>47.050048828125</v>
       </c>
       <c r="Q23">
-        <v>47.050048828125</v>
-      </c>
-      <c r="V23">
-        <v>51.92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>51.919921875</v>
+      </c>
+      <c r="R23">
+        <v>51.919921875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1624,11 +1579,8 @@
       <c r="N24">
         <v>61.39990234375</v>
       </c>
-      <c r="V24">
-        <v>67.55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1671,11 +1623,8 @@
       <c r="N25">
         <v>54.60009765625</v>
       </c>
-      <c r="V25">
-        <v>30.65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1691,11 +1640,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>24.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1708,11 +1654,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>40.63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1762,13 +1705,13 @@
         <v>76.9501953125</v>
       </c>
       <c r="Q28">
-        <v>76.9501953125</v>
-      </c>
-      <c r="V28">
-        <v>61.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>61.169921875</v>
+      </c>
+      <c r="R28">
+        <v>61.169921875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1818,13 +1761,13 @@
         <v>61.679931640625</v>
       </c>
       <c r="Q29">
-        <v>61.679931640625</v>
-      </c>
-      <c r="V29">
-        <v>49.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>49.02001953125</v>
+      </c>
+      <c r="R29">
+        <v>49.02001953125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1874,13 +1817,13 @@
         <v>49.280029296875</v>
       </c>
       <c r="Q30">
-        <v>49.280029296875</v>
-      </c>
-      <c r="V30">
-        <v>54.58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>54.580078125</v>
+      </c>
+      <c r="R30">
+        <v>54.580078125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1930,13 +1873,13 @@
         <v>48.080078125</v>
       </c>
       <c r="Q31">
-        <v>48.080078125</v>
-      </c>
-      <c r="V31">
-        <v>64.92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>64.919921875</v>
+      </c>
+      <c r="R31">
+        <v>64.919921875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1976,11 +1919,8 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-      <c r="V32">
-        <v>57.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -2030,10 +1970,7 @@
         <v>53.139892578125</v>
       </c>
       <c r="Q33">
-        <v>53.139892578125</v>
-      </c>
-      <c r="V33">
-        <v>39.22</v>
+        <v>39.219970703125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -653,6 +653,9 @@
       <c r="P2">
         <v>41.949951171875</v>
       </c>
+      <c r="V2">
+        <v>75.39</v>
+      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -691,6 +694,9 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
+      <c r="V3">
+        <v>72.28</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -747,6 +753,9 @@
       <c r="R4">
         <v>65.60009765625</v>
       </c>
+      <c r="V4">
+        <v>57.68</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1">
@@ -785,6 +794,9 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
+      <c r="V5">
+        <v>84.48999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -832,6 +844,9 @@
       <c r="O6">
         <v>97.7900390625</v>
       </c>
+      <c r="V6">
+        <v>83.5</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -855,6 +870,9 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
+      <c r="V7">
+        <v>67.09999999999999</v>
+      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -911,6 +929,9 @@
       <c r="R8">
         <v>63.75</v>
       </c>
+      <c r="V8">
+        <v>73.08</v>
+      </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1">
@@ -967,6 +988,9 @@
       <c r="R9">
         <v>55.89990234375</v>
       </c>
+      <c r="V9">
+        <v>103.39</v>
+      </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1">
@@ -1023,6 +1047,9 @@
       <c r="R10">
         <v>50.6298828125</v>
       </c>
+      <c r="V10">
+        <v>74.58</v>
+      </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1">
@@ -1070,6 +1097,9 @@
       <c r="O11">
         <v>74.43994140625</v>
       </c>
+      <c r="V11">
+        <v>114</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1126,6 +1156,9 @@
       <c r="R12">
         <v>63.75</v>
       </c>
+      <c r="V12">
+        <v>73.08</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1">
@@ -1152,6 +1185,9 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
+      <c r="V13">
+        <v>73.90000000000001</v>
+      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1163,6 +1199,9 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
+      <c r="V14">
+        <v>74.59999999999999</v>
+      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1204,6 +1243,9 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
+      <c r="V15">
+        <v>74.98</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1233,8 +1275,11 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="V16">
+        <v>75.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1265,8 +1310,11 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="V17">
+        <v>80.04000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1300,8 +1348,11 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="V18">
+        <v>72.09999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1353,8 +1404,11 @@
       <c r="Q19">
         <v>43.72998046875</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="V19">
+        <v>66.58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1403,8 +1457,11 @@
       <c r="P20">
         <v>46.050048828125</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="V20">
+        <v>87.88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1423,8 +1480,11 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="V21">
+        <v>68.69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1479,8 +1539,11 @@
       <c r="R22">
         <v>68.35009765625</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="V22">
+        <v>74.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1535,8 +1598,11 @@
       <c r="R23">
         <v>51.919921875</v>
       </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="V23">
+        <v>64.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1579,8 +1645,11 @@
       <c r="N24">
         <v>61.39990234375</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="V24">
+        <v>88.68000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1623,8 +1692,11 @@
       <c r="N25">
         <v>54.60009765625</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="V25">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1640,8 +1712,11 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="V26">
+        <v>53.89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1654,8 +1729,11 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="V27">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1710,8 +1788,11 @@
       <c r="R28">
         <v>61.169921875</v>
       </c>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="V28">
+        <v>81.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1766,8 +1847,11 @@
       <c r="R29">
         <v>49.02001953125</v>
       </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="V29">
+        <v>69.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1822,8 +1906,11 @@
       <c r="R30">
         <v>54.580078125</v>
       </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="V30">
+        <v>68.58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1878,8 +1965,11 @@
       <c r="R31">
         <v>64.919921875</v>
       </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="V31">
+        <v>81.78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -1919,8 +2009,11 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="V32">
+        <v>72.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -1971,6 +2064,9 @@
       </c>
       <c r="Q33">
         <v>39.219970703125</v>
+      </c>
+      <c r="V33">
+        <v>114.29</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 16</t>
+    <t>Parcial Rodada 17</t>
   </si>
   <si>
     <t>time_id</t>
@@ -653,9 +653,6 @@
       <c r="P2">
         <v>41.949951171875</v>
       </c>
-      <c r="V2">
-        <v>75.39</v>
-      </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="1">
@@ -694,9 +691,6 @@
       <c r="L3">
         <v>39.469970703125</v>
       </c>
-      <c r="V3">
-        <v>72.28</v>
-      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1">
@@ -751,10 +745,7 @@
         <v>65.60009765625</v>
       </c>
       <c r="R4">
-        <v>65.60009765625</v>
-      </c>
-      <c r="V4">
-        <v>57.68</v>
+        <v>57.679931640625</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -794,9 +785,6 @@
       <c r="L5">
         <v>46.590087890625</v>
       </c>
-      <c r="V5">
-        <v>84.48999999999999</v>
-      </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1">
@@ -844,9 +832,6 @@
       <c r="O6">
         <v>97.7900390625</v>
       </c>
-      <c r="V6">
-        <v>83.5</v>
-      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="1">
@@ -870,9 +855,6 @@
       <c r="G7">
         <v>69.3701171875</v>
       </c>
-      <c r="V7">
-        <v>67.09999999999999</v>
-      </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1">
@@ -927,10 +909,10 @@
         <v>63.75</v>
       </c>
       <c r="R8">
-        <v>63.75</v>
-      </c>
-      <c r="V8">
-        <v>73.08</v>
+        <v>73.080078125</v>
+      </c>
+      <c r="S8">
+        <v>73.080078125</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -986,10 +968,10 @@
         <v>55.89990234375</v>
       </c>
       <c r="R9">
-        <v>55.89990234375</v>
-      </c>
-      <c r="V9">
-        <v>103.39</v>
+        <v>103.39013671875</v>
+      </c>
+      <c r="S9">
+        <v>103.39013671875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1045,10 +1027,10 @@
         <v>50.6298828125</v>
       </c>
       <c r="R10">
-        <v>50.6298828125</v>
-      </c>
-      <c r="V10">
-        <v>74.58</v>
+        <v>74.580078125</v>
+      </c>
+      <c r="S10">
+        <v>74.580078125</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1097,9 +1079,6 @@
       <c r="O11">
         <v>74.43994140625</v>
       </c>
-      <c r="V11">
-        <v>114</v>
-      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1">
@@ -1154,10 +1133,10 @@
         <v>63.75</v>
       </c>
       <c r="R12">
-        <v>63.75</v>
-      </c>
-      <c r="V12">
-        <v>73.08</v>
+        <v>73.080078125</v>
+      </c>
+      <c r="S12">
+        <v>73.080078125</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1185,9 +1164,6 @@
       <c r="H13">
         <v>44.510009765625</v>
       </c>
-      <c r="V13">
-        <v>73.90000000000001</v>
-      </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1">
@@ -1199,9 +1175,6 @@
       <c r="C14">
         <v>42.9599609375</v>
       </c>
-      <c r="V14">
-        <v>74.59999999999999</v>
-      </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1">
@@ -1243,9 +1216,6 @@
       <c r="M15">
         <v>70.16015625</v>
       </c>
-      <c r="V15">
-        <v>74.98</v>
-      </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1">
@@ -1275,11 +1245,8 @@
       <c r="I16">
         <v>49.469970703125</v>
       </c>
-      <c r="V16">
-        <v>75.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1310,11 +1277,8 @@
       <c r="J17">
         <v>45.699951171875</v>
       </c>
-      <c r="V17">
-        <v>80.04000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1348,11 +1312,8 @@
       <c r="K18">
         <v>56.090087890625</v>
       </c>
-      <c r="V18">
-        <v>72.09999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1404,11 +1365,8 @@
       <c r="Q19">
         <v>43.72998046875</v>
       </c>
-      <c r="V19">
-        <v>66.58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1457,11 +1415,8 @@
       <c r="P20">
         <v>46.050048828125</v>
       </c>
-      <c r="V20">
-        <v>87.88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1480,11 +1435,8 @@
       <c r="F21">
         <v>27.4300537109375</v>
       </c>
-      <c r="V21">
-        <v>68.69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1537,13 +1489,13 @@
         <v>68.35009765625</v>
       </c>
       <c r="R22">
-        <v>68.35009765625</v>
-      </c>
-      <c r="V22">
-        <v>74.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>74.27978515625</v>
+      </c>
+      <c r="S22">
+        <v>74.27978515625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1596,13 +1548,10 @@
         <v>51.919921875</v>
       </c>
       <c r="R23">
-        <v>51.919921875</v>
-      </c>
-      <c r="V23">
-        <v>64.38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>64.3798828125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1645,11 +1594,8 @@
       <c r="N24">
         <v>61.39990234375</v>
       </c>
-      <c r="V24">
-        <v>88.68000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1692,11 +1638,8 @@
       <c r="N25">
         <v>54.60009765625</v>
       </c>
-      <c r="V25">
-        <v>67.09999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1712,11 +1655,8 @@
       <c r="E26">
         <v>65.259765625</v>
       </c>
-      <c r="V26">
-        <v>53.89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1729,11 +1669,8 @@
       <c r="D27">
         <v>36.429931640625</v>
       </c>
-      <c r="V27">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1786,13 +1723,13 @@
         <v>61.169921875</v>
       </c>
       <c r="R28">
-        <v>61.169921875</v>
-      </c>
-      <c r="V28">
-        <v>81.28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>81.27978515625</v>
+      </c>
+      <c r="S28">
+        <v>81.27978515625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1845,13 +1782,13 @@
         <v>49.02001953125</v>
       </c>
       <c r="R29">
-        <v>49.02001953125</v>
-      </c>
-      <c r="V29">
-        <v>69.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>69.77978515625</v>
+      </c>
+      <c r="S29">
+        <v>69.77978515625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1904,13 +1841,13 @@
         <v>54.580078125</v>
       </c>
       <c r="R30">
-        <v>54.580078125</v>
-      </c>
-      <c r="V30">
-        <v>68.58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>68.580078125</v>
+      </c>
+      <c r="S30">
+        <v>68.580078125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1963,13 +1900,13 @@
         <v>64.919921875</v>
       </c>
       <c r="R31">
-        <v>64.919921875</v>
-      </c>
-      <c r="V31">
-        <v>81.78</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>81.77978515625</v>
+      </c>
+      <c r="S31">
+        <v>81.77978515625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
@@ -2009,11 +1946,8 @@
       <c r="M32">
         <v>69.25</v>
       </c>
-      <c r="V32">
-        <v>72.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="1">
         <v>51010813</v>
       </c>
@@ -2064,9 +1998,6 @@
       </c>
       <c r="Q33">
         <v>39.219970703125</v>
-      </c>
-      <c r="V33">
-        <v>114.29</v>
       </c>
     </row>
   </sheetData>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 17</t>
+    <t>Parcial Rodada 18</t>
   </si>
   <si>
     <t>time_id</t>
@@ -912,7 +912,10 @@
         <v>73.080078125</v>
       </c>
       <c r="S8">
-        <v>73.080078125</v>
+        <v>65.6201171875</v>
+      </c>
+      <c r="T8">
+        <v>65.6201171875</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -971,7 +974,7 @@
         <v>103.39013671875</v>
       </c>
       <c r="S9">
-        <v>103.39013671875</v>
+        <v>60.1201171875</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1030,7 +1033,10 @@
         <v>74.580078125</v>
       </c>
       <c r="S10">
-        <v>74.580078125</v>
+        <v>84.919921875</v>
+      </c>
+      <c r="T10">
+        <v>84.919921875</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1136,7 +1142,10 @@
         <v>73.080078125</v>
       </c>
       <c r="S12">
-        <v>73.080078125</v>
+        <v>65.6201171875</v>
+      </c>
+      <c r="T12">
+        <v>65.6201171875</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1246,7 +1255,7 @@
         <v>49.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:20">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>45.699951171875</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:20">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1313,7 +1322,7 @@
         <v>56.090087890625</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:20">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1366,7 +1375,7 @@
         <v>43.72998046875</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:20">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1416,7 +1425,7 @@
         <v>46.050048828125</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:20">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1436,7 +1445,7 @@
         <v>27.4300537109375</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:20">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1492,10 +1501,13 @@
         <v>74.27978515625</v>
       </c>
       <c r="S22">
-        <v>74.27978515625</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+        <v>71.6201171875</v>
+      </c>
+      <c r="T22">
+        <v>71.6201171875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1551,7 +1563,7 @@
         <v>64.3798828125</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:20">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1595,7 +1607,7 @@
         <v>61.39990234375</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:20">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1639,7 +1651,7 @@
         <v>54.60009765625</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:20">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1656,7 +1668,7 @@
         <v>65.259765625</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:20">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1670,7 +1682,7 @@
         <v>36.429931640625</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:20">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1726,10 +1738,13 @@
         <v>81.27978515625</v>
       </c>
       <c r="S28">
-        <v>81.27978515625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+        <v>92.31982421875</v>
+      </c>
+      <c r="T28">
+        <v>92.31982421875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1785,10 +1800,13 @@
         <v>69.77978515625</v>
       </c>
       <c r="S29">
-        <v>69.77978515625</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
+        <v>93.22021484375</v>
+      </c>
+      <c r="T29">
+        <v>93.22021484375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1844,10 +1862,13 @@
         <v>68.580078125</v>
       </c>
       <c r="S30">
-        <v>68.580078125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19">
+        <v>70.81982421875</v>
+      </c>
+      <c r="T30">
+        <v>70.81982421875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1903,10 +1924,10 @@
         <v>81.77978515625</v>
       </c>
       <c r="S31">
-        <v>81.77978515625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19">
+        <v>59.1201171875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>

--- a/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/Pontuacoes_Por_Rodada_Liga_Eliminacao.xlsx
@@ -76,7 +76,7 @@
     <t>Rodada 19</t>
   </si>
   <si>
-    <t>Parcial Rodada 18</t>
+    <t>Parcial Rodada 19</t>
   </si>
   <si>
     <t>time_id</t>
@@ -915,7 +915,10 @@
         <v>65.6201171875</v>
       </c>
       <c r="T8">
-        <v>65.6201171875</v>
+        <v>111.64990234375</v>
+      </c>
+      <c r="U8">
+        <v>111.64990234375</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1036,7 +1039,10 @@
         <v>84.919921875</v>
       </c>
       <c r="T10">
-        <v>84.919921875</v>
+        <v>122.75</v>
+      </c>
+      <c r="U10">
+        <v>122.75</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1145,7 +1151,10 @@
         <v>65.6201171875</v>
       </c>
       <c r="T12">
-        <v>65.6201171875</v>
+        <v>109.5</v>
+      </c>
+      <c r="U12">
+        <v>109.5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1255,7 +1264,7 @@
         <v>49.469970703125</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:21">
       <c r="A17" s="1">
         <v>14124559</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>45.699951171875</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:21">
       <c r="A18" s="1">
         <v>18223508</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>56.090087890625</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:21">
       <c r="A19" s="1">
         <v>18344271</v>
       </c>
@@ -1375,7 +1384,7 @@
         <v>43.72998046875</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:21">
       <c r="A20" s="1">
         <v>18642587</v>
       </c>
@@ -1425,7 +1434,7 @@
         <v>46.050048828125</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:21">
       <c r="A21" s="1">
         <v>18661583</v>
       </c>
@@ -1445,7 +1454,7 @@
         <v>27.4300537109375</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:21">
       <c r="A22" s="1">
         <v>19033717</v>
       </c>
@@ -1504,10 +1513,10 @@
         <v>71.6201171875</v>
       </c>
       <c r="T22">
-        <v>71.6201171875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="1">
         <v>20696550</v>
       </c>
@@ -1563,7 +1572,7 @@
         <v>64.3798828125</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:21">
       <c r="A24" s="1">
         <v>24468241</v>
       </c>
@@ -1607,7 +1616,7 @@
         <v>61.39990234375</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:21">
       <c r="A25" s="1">
         <v>24856400</v>
       </c>
@@ -1651,7 +1660,7 @@
         <v>54.60009765625</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:21">
       <c r="A26" s="1">
         <v>25565675</v>
       </c>
@@ -1668,7 +1677,7 @@
         <v>65.259765625</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:21">
       <c r="A27" s="1">
         <v>25811332</v>
       </c>
@@ -1682,7 +1691,7 @@
         <v>36.429931640625</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:21">
       <c r="A28" s="1">
         <v>28741323</v>
       </c>
@@ -1741,10 +1750,13 @@
         <v>92.31982421875</v>
       </c>
       <c r="T28">
-        <v>92.31982421875</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>113.4501953125</v>
+      </c>
+      <c r="U28">
+        <v>113.4501953125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" s="1">
         <v>29228373</v>
       </c>
@@ -1803,10 +1815,13 @@
         <v>93.22021484375</v>
       </c>
       <c r="T29">
-        <v>93.22021484375</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>136.400390625</v>
+      </c>
+      <c r="U29">
+        <v>136.400390625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" s="1">
         <v>44810918</v>
       </c>
@@ -1865,10 +1880,10 @@
         <v>70.81982421875</v>
       </c>
       <c r="T30">
-        <v>70.81982421875</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>106.10009765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" s="1">
         <v>47544767</v>
       </c>
@@ -1927,7 +1942,7 @@
         <v>59.1201171875</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:21">
       <c r="A32" s="1">
         <v>48498051</v>
       </c>
